--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -417,14 +417,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="33" customWidth="1" min="8" max="8"/>
@@ -493,23 +493,23 @@
         <v>16.4</v>
       </c>
       <c r="D2" t="n">
-        <v>16.49</v>
+        <v>14.31</v>
       </c>
       <c r="E2" t="n">
         <v>16</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.5%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+3.0%</t>
+          <t>-10.6%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>148415</v>
+        <v>315444</v>
       </c>
       <c r="I2" t="n">
         <v>2.79</v>
@@ -530,26 +530,26 @@
         <v>47.7</v>
       </c>
       <c r="D3" t="n">
-        <v>42.56</v>
+        <v>36.66</v>
       </c>
       <c r="E3" t="n">
         <v>45</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-10.8%</t>
+          <t>-23.1%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-18.5%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>207393</v>
+        <v>299841</v>
       </c>
       <c r="I3" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="4">
@@ -567,23 +567,23 @@
         <v>34.5</v>
       </c>
       <c r="D4" t="n">
-        <v>31.37</v>
+        <v>27.09</v>
       </c>
       <c r="E4" t="n">
         <v>30.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-21.5%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+2.8%</t>
+          <t>-11.2%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>207932</v>
+        <v>311398</v>
       </c>
       <c r="I4" t="n">
         <v>2.57</v>
@@ -601,29 +601,29 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>53.32436398628737</v>
+        <v>50.94942281238824</v>
       </c>
       <c r="D5" t="n">
-        <v>42.18</v>
+        <v>37.34</v>
       </c>
       <c r="E5" t="n">
-        <v>54.3498325244852</v>
+        <v>51.92921940493417</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-26.7%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-22.4%</t>
+          <t>-28.1%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>303978</v>
+        <v>341877</v>
       </c>
       <c r="I5" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="6">
@@ -641,19 +641,19 @@
         <v>70.8</v>
       </c>
       <c r="D6" t="n">
-        <v>79.13</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="E6" t="n">
         <v>75</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+11.8%</t>
+          <t>+4.5%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+5.5%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -678,23 +678,23 @@
         <v>5.2</v>
       </c>
       <c r="D7" t="n">
-        <v>3.09</v>
+        <v>2.6</v>
       </c>
       <c r="E7" t="n">
         <v>6</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-40.7%</t>
+          <t>-50.0%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-48.6%</t>
+          <t>-56.7%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>287175</v>
+        <v>333611</v>
       </c>
       <c r="I7" t="n">
         <v>2.21</v>
@@ -789,26 +789,26 @@
         <v>75.59999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>77.29000000000001</v>
+        <v>74</v>
       </c>
       <c r="E10" t="n">
         <v>94</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+2.2%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-21.3%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2725019</v>
       </c>
       <c r="I10" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="11">
@@ -826,23 +826,23 @@
         <v>7.7</v>
       </c>
       <c r="D11" t="n">
-        <v>5.7</v>
+        <v>5.59</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-26.0%</t>
+          <t>-27.4%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-43.0%</t>
+          <t>-44.1%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>123511</v>
+        <v>126273</v>
       </c>
       <c r="I11" t="n">
         <v>1.66</v>
@@ -863,26 +863,26 @@
         <v>28.2</v>
       </c>
       <c r="D12" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="E12" t="n">
         <v>25</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+9.1%</t>
+          <t>+4.4%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>58812</v>
+        <v>68988</v>
       </c>
       <c r="I12" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="13">
@@ -900,26 +900,26 @@
         <v>16</v>
       </c>
       <c r="D13" t="n">
-        <v>14.9</v>
+        <v>14.88</v>
       </c>
       <c r="E13" t="n">
         <v>17.95</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>38252</v>
+        <v>38532</v>
       </c>
       <c r="I13" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="14">
@@ -937,26 +937,63 @@
         <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>58.42</v>
+        <v>53.31</v>
       </c>
       <c r="E14" t="n">
         <v>51.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+32.8%</t>
+          <t>+21.2%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+13.4%</t>
+          <t>+3.5%</t>
         </is>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>25.66</v>
+      </c>
+      <c r="E15" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-5.7%</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-25.6%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>28969</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -990,10 +990,47 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>28969</v>
+        <v>28968</v>
       </c>
       <c r="I15" t="n">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>GNK</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>24</v>
+      </c>
+      <c r="D16" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>+5.0%</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>+1.6%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>18726</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -530,7 +530,7 @@
         <v>47.7</v>
       </c>
       <c r="D3" t="n">
-        <v>36.66</v>
+        <v>36.67</v>
       </c>
       <c r="E3" t="n">
         <v>45</v>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>299841</v>
+        <v>299660</v>
       </c>
       <c r="I3" t="n">
         <v>2.5</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>311398</v>
+        <v>311332</v>
       </c>
       <c r="I4" t="n">
         <v>2.57</v>
@@ -601,13 +601,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50.94942281238824</v>
+        <v>50.93591183222913</v>
       </c>
       <c r="D5" t="n">
-        <v>37.34</v>
+        <v>37.32</v>
       </c>
       <c r="E5" t="n">
-        <v>51.92921940493417</v>
+        <v>51.91544859823353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>341877</v>
+        <v>342121</v>
       </c>
       <c r="I5" t="n">
         <v>2.4</v>
@@ -641,14 +641,14 @@
         <v>70.8</v>
       </c>
       <c r="D6" t="n">
-        <v>73.95999999999999</v>
+        <v>73.92</v>
       </c>
       <c r="E6" t="n">
         <v>75</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+4.5%</t>
+          <t>+4.4%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -678,23 +678,23 @@
         <v>5.2</v>
       </c>
       <c r="D7" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="E7" t="n">
         <v>6</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>-50.1%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-56.7%</t>
+          <t>-56.8%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>333611</v>
+        <v>334239</v>
       </c>
       <c r="I7" t="n">
         <v>2.21</v>
@@ -937,7 +937,7 @@
         <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>53.31</v>
+        <v>53.32</v>
       </c>
       <c r="E14" t="n">
         <v>51.5</v>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -974,23 +974,23 @@
         <v>27.2</v>
       </c>
       <c r="D15" t="n">
-        <v>25.66</v>
+        <v>25.74</v>
       </c>
       <c r="E15" t="n">
         <v>34.5</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-25.6%</t>
+          <t>-25.4%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>28968</v>
+        <v>28583</v>
       </c>
       <c r="I15" t="n">
         <v>1.23</v>
@@ -1011,23 +1011,23 @@
         <v>24</v>
       </c>
       <c r="D16" t="n">
-        <v>25.2</v>
+        <v>25.28</v>
       </c>
       <c r="E16" t="n">
         <v>24.8</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+5.0%</t>
+          <t>+5.3%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+1.6%</t>
+          <t>+1.9%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>18726</v>
+        <v>18314</v>
       </c>
       <c r="I16" t="n">
         <v>1.14</v>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -962,7 +962,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -971,65 +971,102 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27.2</v>
+        <v>17.25</v>
       </c>
       <c r="D15" t="n">
-        <v>25.74</v>
+        <v>28.35</v>
       </c>
       <c r="E15" t="n">
-        <v>34.5</v>
+        <v>27.98</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>+64.3%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-25.4%</t>
+          <t>+1.3%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>28583</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>25.74</v>
+      </c>
+      <c r="E16" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-5.4%</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-25.4%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>28583</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>GNK</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>whole-company</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
         <v>24</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D17" t="n">
         <v>25.28</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E17" t="n">
         <v>24.8</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>+5.3%</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>+1.9%</t>
         </is>
       </c>
-      <c r="H16" t="n">
+      <c r="H17" t="n">
         <v>18314</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I17" t="n">
         <v>1.14</v>
       </c>
     </row>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -974,19 +974,19 @@
         <v>17.25</v>
       </c>
       <c r="D15" t="n">
-        <v>28.35</v>
+        <v>19.84</v>
       </c>
       <c r="E15" t="n">
         <v>27.98</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+64.3%</t>
+          <t>+15.0%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+1.3%</t>
+          <t>-29.1%</t>
         </is>
       </c>
       <c r="H15" t="n">

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.4</v>
+        <v>16.6</v>
       </c>
       <c r="D2" t="n">
         <v>14.31</v>
@@ -500,7 +500,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-13.8%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>315444</v>
+        <v>330771</v>
       </c>
       <c r="I2" t="n">
         <v>2.79</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>47.7</v>
+        <v>49.2</v>
       </c>
       <c r="D3" t="n">
         <v>36.67</v>
@@ -537,7 +537,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-23.1%</t>
+          <t>-25.5%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>299660</v>
+        <v>324117</v>
       </c>
       <c r="I3" t="n">
         <v>2.5</v>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>34.5</v>
+        <v>36.28</v>
       </c>
       <c r="D4" t="n">
         <v>27.09</v>
@@ -574,7 +574,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-21.5%</t>
+          <t>-25.3%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>311332</v>
+        <v>354881</v>
       </c>
       <c r="I4" t="n">
         <v>2.57</v>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50.93591183222913</v>
+        <v>53.94635482641601</v>
       </c>
       <c r="D5" t="n">
         <v>37.32</v>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-26.7%</t>
+          <t>-30.8%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>342121</v>
+        <v>393378</v>
       </c>
       <c r="I5" t="n">
         <v>2.4</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>70.8</v>
+        <v>72.76000000000001</v>
       </c>
       <c r="D6" t="n">
         <v>73.92</v>
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+4.4%</t>
+          <t>+1.6%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>47855</v>
       </c>
       <c r="I6" t="n">
         <v>2.15</v>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5.2</v>
+        <v>5.18</v>
       </c>
       <c r="D7" t="n">
         <v>2.59</v>
@@ -685,7 +685,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-50.1%</t>
+          <t>-49.9%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>334239</v>
+        <v>332327</v>
       </c>
       <c r="I7" t="n">
         <v>2.21</v>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>29.7</v>
+        <v>30.34</v>
       </c>
       <c r="D8" t="n">
         <v>26.27</v>
@@ -722,7 +722,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-13.4%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.9</v>
+        <v>21.46</v>
       </c>
       <c r="D9" t="n">
         <v>22.88</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+4.5%</t>
+          <t>+6.6%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>75.59999999999999</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="D10" t="n">
         <v>74</v>
@@ -796,7 +796,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7.7</v>
+        <v>7.36</v>
       </c>
       <c r="D11" t="n">
         <v>5.59</v>
@@ -833,7 +833,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-24.0%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>126273</v>
+        <v>113530</v>
       </c>
       <c r="I11" t="n">
         <v>1.66</v>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>28.2</v>
+        <v>29.18</v>
       </c>
       <c r="D12" t="n">
         <v>26.09</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-10.6%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>68988</v>
+        <v>78345</v>
       </c>
       <c r="I12" t="n">
         <v>1.68</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16</v>
+        <v>16.43</v>
       </c>
       <c r="D13" t="n">
         <v>14.88</v>
@@ -907,7 +907,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>38532</v>
+        <v>43825</v>
       </c>
       <c r="I13" t="n">
         <v>1.37</v>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>37.14</v>
       </c>
       <c r="D14" t="n">
         <v>53.32</v>
@@ -944,7 +944,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+21.2%</t>
+          <t>+43.6%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.25</v>
+        <v>17.24</v>
       </c>
       <c r="D15" t="n">
         <v>19.84</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+15.0%</t>
+          <t>+15.1%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>27.2</v>
+        <v>26.57</v>
       </c>
       <c r="D16" t="n">
         <v>25.74</v>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>28583</v>
+        <v>25856</v>
       </c>
       <c r="I16" t="n">
         <v>1.23</v>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24</v>
+        <v>23.5</v>
       </c>
       <c r="D17" t="n">
         <v>25.28</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+5.3%</t>
+          <t>+7.6%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>18314</v>
+        <v>15736</v>
       </c>
       <c r="I17" t="n">
         <v>1.14</v>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -417,12 +417,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.6</v>
+        <v>16.925</v>
       </c>
       <c r="D2" t="n">
         <v>14.31</v>
@@ -500,7 +500,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-13.8%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>330771</v>
+        <v>355677</v>
       </c>
       <c r="I2" t="n">
         <v>2.79</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>49.2</v>
+        <v>50.57</v>
       </c>
       <c r="D3" t="n">
         <v>36.67</v>
@@ -537,7 +537,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-25.5%</t>
+          <t>-27.5%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>324117</v>
+        <v>346455</v>
       </c>
       <c r="I3" t="n">
         <v>2.5</v>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>36.28</v>
+        <v>38.08</v>
       </c>
       <c r="D4" t="n">
         <v>27.09</v>
@@ -574,7 +574,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-25.3%</t>
+          <t>-28.8%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>354881</v>
+        <v>398919</v>
       </c>
       <c r="I4" t="n">
         <v>2.57</v>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>53.94635482641601</v>
+        <v>55.04670112689429</v>
       </c>
       <c r="D5" t="n">
         <v>37.32</v>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-30.8%</t>
+          <t>-32.2%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>393378</v>
+        <v>412112</v>
       </c>
       <c r="I5" t="n">
         <v>2.4</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>72.76000000000001</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="D6" t="n">
         <v>73.92</v>
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+1.6%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>47855</v>
+        <v>88915</v>
       </c>
       <c r="I6" t="n">
         <v>2.15</v>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5.18</v>
+        <v>5.26</v>
       </c>
       <c r="D7" t="n">
         <v>2.59</v>
@@ -685,7 +685,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-49.9%</t>
+          <t>-50.7%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>332327</v>
+        <v>339977</v>
       </c>
       <c r="I7" t="n">
         <v>2.21</v>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>30.34</v>
+        <v>31.098</v>
       </c>
       <c r="D8" t="n">
         <v>26.27</v>
@@ -722,7 +722,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-13.4%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.46</v>
+        <v>22.2</v>
       </c>
       <c r="D9" t="n">
         <v>22.88</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+6.6%</t>
+          <t>+3.0%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>76.45999999999999</v>
+        <v>77.94</v>
       </c>
       <c r="D10" t="n">
         <v>74</v>
@@ -796,7 +796,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7.36</v>
+        <v>7.44</v>
       </c>
       <c r="D11" t="n">
         <v>5.59</v>
@@ -833,7 +833,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-24.0%</t>
+          <t>-24.9%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>113530</v>
+        <v>116528</v>
       </c>
       <c r="I11" t="n">
         <v>1.66</v>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29.18</v>
+        <v>29.98</v>
       </c>
       <c r="D12" t="n">
         <v>26.09</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>78345</v>
+        <v>85983</v>
       </c>
       <c r="I12" t="n">
         <v>1.68</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.43</v>
+        <v>16.89</v>
       </c>
       <c r="D13" t="n">
         <v>14.88</v>
@@ -907,7 +907,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>43825</v>
+        <v>49486</v>
       </c>
       <c r="I13" t="n">
         <v>1.37</v>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>37.14</v>
+        <v>37.99</v>
       </c>
       <c r="D14" t="n">
         <v>53.32</v>
@@ -944,7 +944,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+43.6%</t>
+          <t>+40.3%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.24</v>
+        <v>17.39</v>
       </c>
       <c r="D15" t="n">
         <v>19.84</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+15.1%</t>
+          <t>+14.1%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>26.57</v>
+        <v>27.06</v>
       </c>
       <c r="D16" t="n">
         <v>25.74</v>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>25856</v>
+        <v>27977</v>
       </c>
       <c r="I16" t="n">
         <v>1.23</v>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.5</v>
+        <v>23.805</v>
       </c>
       <c r="D17" t="n">
         <v>25.28</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+7.6%</t>
+          <t>+6.2%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1064,10 +1064,47 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>15736</v>
+        <v>17309</v>
       </c>
       <c r="I17" t="n">
         <v>1.14</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CAPT</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>12.74</v>
+      </c>
+      <c r="D18" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="E18" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>+31.2%</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-11.6%</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -937,26 +937,26 @@
         <v>37.99</v>
       </c>
       <c r="D14" t="n">
-        <v>53.32</v>
+        <v>58.09</v>
       </c>
       <c r="E14" t="n">
         <v>51.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+40.3%</t>
+          <t>+52.9%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+3.5%</t>
+          <t>+12.8%</t>
         </is>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="15">

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.925</v>
+        <v>16.65</v>
       </c>
       <c r="D2" t="n">
         <v>14.31</v>
@@ -500,7 +500,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-14.1%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>355677</v>
+        <v>334603</v>
       </c>
       <c r="I2" t="n">
         <v>2.79</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>50.57</v>
+        <v>49.76</v>
       </c>
       <c r="D3" t="n">
         <v>36.67</v>
@@ -537,7 +537,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-27.5%</t>
+          <t>-26.3%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>346455</v>
+        <v>333248</v>
       </c>
       <c r="I3" t="n">
         <v>2.5</v>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>38.08</v>
+        <v>37.13</v>
       </c>
       <c r="D4" t="n">
         <v>27.09</v>
@@ -574,7 +574,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-28.8%</t>
+          <t>-27.0%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>398919</v>
+        <v>375677</v>
       </c>
       <c r="I4" t="n">
         <v>2.57</v>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>55.04670112689429</v>
+        <v>53.91370360088253</v>
       </c>
       <c r="D5" t="n">
         <v>37.32</v>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-32.2%</t>
+          <t>-30.8%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>412112</v>
+        <v>392822</v>
       </c>
       <c r="I5" t="n">
         <v>2.4</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>74.06999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="D6" t="n">
         <v>73.92</v>
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>+2.0%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>88915</v>
+        <v>39706</v>
       </c>
       <c r="I6" t="n">
         <v>2.15</v>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5.26</v>
+        <v>5.15</v>
       </c>
       <c r="D7" t="n">
         <v>2.59</v>
@@ -685,7 +685,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-50.7%</t>
+          <t>-49.6%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>339977</v>
+        <v>329458</v>
       </c>
       <c r="I7" t="n">
         <v>2.21</v>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>31.098</v>
+        <v>30.5</v>
       </c>
       <c r="D8" t="n">
         <v>26.27</v>
@@ -722,7 +722,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-13.9%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.2</v>
+        <v>21.51</v>
       </c>
       <c r="D9" t="n">
         <v>22.88</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+3.0%</t>
+          <t>+6.3%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>77.94</v>
+        <v>76.17</v>
       </c>
       <c r="D10" t="n">
         <v>74</v>
@@ -796,7 +796,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7.44</v>
+        <v>7.28</v>
       </c>
       <c r="D11" t="n">
         <v>5.59</v>
@@ -833,7 +833,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-24.9%</t>
+          <t>-23.2%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>116528</v>
+        <v>110531</v>
       </c>
       <c r="I11" t="n">
         <v>1.66</v>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29.98</v>
+        <v>28.95</v>
       </c>
       <c r="D12" t="n">
         <v>26.09</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-9.9%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>85983</v>
+        <v>76149</v>
       </c>
       <c r="I12" t="n">
         <v>1.68</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.89</v>
+        <v>16.38</v>
       </c>
       <c r="D13" t="n">
         <v>14.88</v>
@@ -907,7 +907,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-9.2%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>49486</v>
+        <v>43209</v>
       </c>
       <c r="I13" t="n">
         <v>1.37</v>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>37.99</v>
+        <v>37.11</v>
       </c>
       <c r="D14" t="n">
         <v>58.09</v>
@@ -944,7 +944,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+52.9%</t>
+          <t>+56.5%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.39</v>
+        <v>17.6</v>
       </c>
       <c r="D15" t="n">
         <v>19.84</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+14.1%</t>
+          <t>+12.7%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>27.06</v>
+        <v>27.15</v>
       </c>
       <c r="D16" t="n">
         <v>25.74</v>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>27977</v>
+        <v>28367</v>
       </c>
       <c r="I16" t="n">
         <v>1.23</v>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.805</v>
+        <v>23.69</v>
       </c>
       <c r="D17" t="n">
         <v>25.28</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+6.2%</t>
+          <t>+6.7%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>17309</v>
+        <v>16716</v>
       </c>
       <c r="I17" t="n">
         <v>1.14</v>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>12.74</v>
+        <v>12.79</v>
       </c>
       <c r="D18" t="n">
         <v>16.71</v>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+31.2%</t>
+          <t>+30.7%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1107,6 +1107,80 @@
         <v>2.5</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MPCC</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-23.4%</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-19.0%</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>350590</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>38.99</v>
+      </c>
+      <c r="D20" t="n">
+        <v>33.61</v>
+      </c>
+      <c r="E20" t="n">
+        <v>52.04</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-13.8%</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-35.4%</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>2757173</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -424,7 +424,7 @@
     <col width="32" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="33" customWidth="1" min="8" max="8"/>
@@ -601,13 +601,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>53.91370360088253</v>
+        <v>53.90889664553365</v>
       </c>
       <c r="D5" t="n">
-        <v>37.32</v>
+        <v>37.31</v>
       </c>
       <c r="E5" t="n">
-        <v>51.91544859823353</v>
+        <v>51.91081980765414</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>392822</v>
+        <v>392865</v>
       </c>
       <c r="I5" t="n">
         <v>2.4</v>
@@ -641,7 +641,7 @@
         <v>72.5</v>
       </c>
       <c r="D6" t="n">
-        <v>73.92</v>
+        <v>73.94</v>
       </c>
       <c r="E6" t="n">
         <v>75</v>
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>39706</v>
+        <v>39131</v>
       </c>
       <c r="I6" t="n">
         <v>2.15</v>
@@ -937,19 +937,19 @@
         <v>37.11</v>
       </c>
       <c r="D14" t="n">
-        <v>58.09</v>
+        <v>57.74</v>
       </c>
       <c r="E14" t="n">
         <v>51.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+56.5%</t>
+          <t>+55.6%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+12.8%</t>
+          <t>+12.1%</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -974,19 +974,19 @@
         <v>17.6</v>
       </c>
       <c r="D15" t="n">
-        <v>19.84</v>
+        <v>20</v>
       </c>
       <c r="E15" t="n">
         <v>27.98</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+12.7%</t>
+          <t>+13.6%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-29.1%</t>
+          <t>-28.5%</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1011,23 +1011,23 @@
         <v>27.15</v>
       </c>
       <c r="D16" t="n">
-        <v>25.74</v>
+        <v>26</v>
       </c>
       <c r="E16" t="n">
         <v>34.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-25.4%</t>
+          <t>-24.6%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>28367</v>
+        <v>27187</v>
       </c>
       <c r="I16" t="n">
         <v>1.23</v>
@@ -1048,23 +1048,23 @@
         <v>23.69</v>
       </c>
       <c r="D17" t="n">
-        <v>25.28</v>
+        <v>25.3</v>
       </c>
       <c r="E17" t="n">
         <v>24.8</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+6.7%</t>
+          <t>+6.8%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+1.9%</t>
+          <t>+2.0%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>16716</v>
+        <v>16592</v>
       </c>
       <c r="I17" t="n">
         <v>1.14</v>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -417,12 +417,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.65</v>
+        <v>18.89</v>
       </c>
       <c r="D2" t="n">
         <v>14.31</v>
@@ -500,7 +500,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-14.1%</t>
+          <t>-24.3%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>334603</v>
+        <v>506266</v>
       </c>
       <c r="I2" t="n">
         <v>2.79</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>49.76</v>
+        <v>52.48</v>
       </c>
       <c r="D3" t="n">
         <v>36.67</v>
@@ -537,7 +537,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-26.3%</t>
+          <t>-30.1%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>333248</v>
+        <v>377597</v>
       </c>
       <c r="I3" t="n">
         <v>2.5</v>
@@ -564,26 +564,26 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>37.13</v>
+        <v>40.93</v>
       </c>
       <c r="D4" t="n">
-        <v>27.09</v>
+        <v>26.93</v>
       </c>
       <c r="E4" t="n">
         <v>30.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-27.0%</t>
+          <t>-34.2%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-11.2%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>375677</v>
+        <v>472015</v>
       </c>
       <c r="I4" t="n">
         <v>2.57</v>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>53.90889664553365</v>
+        <v>55.1691215792289</v>
       </c>
       <c r="D5" t="n">
         <v>37.31</v>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-30.8%</t>
+          <t>-32.4%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>392865</v>
+        <v>414323</v>
       </c>
       <c r="I5" t="n">
         <v>2.4</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>72.5</v>
+        <v>74.45</v>
       </c>
       <c r="D6" t="n">
         <v>73.94</v>
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+2.0%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>39131</v>
+        <v>100249</v>
       </c>
       <c r="I6" t="n">
         <v>2.15</v>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5.15</v>
+        <v>5.85</v>
       </c>
       <c r="D7" t="n">
         <v>2.59</v>
@@ -685,7 +685,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-49.6%</t>
+          <t>-55.7%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>329458</v>
+        <v>396401</v>
       </c>
       <c r="I7" t="n">
         <v>2.21</v>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>30.5</v>
+        <v>29.74</v>
       </c>
       <c r="D8" t="n">
         <v>26.27</v>
@@ -722,7 +722,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-13.9%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.51</v>
+        <v>20.03</v>
       </c>
       <c r="D9" t="n">
         <v>22.88</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+6.3%</t>
+          <t>+14.2%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>76.17</v>
+        <v>80.58</v>
       </c>
       <c r="D10" t="n">
         <v>74</v>
@@ -796,7 +796,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7.28</v>
+        <v>7.23</v>
       </c>
       <c r="D11" t="n">
         <v>5.59</v>
@@ -833,7 +833,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-23.2%</t>
+          <t>-22.7%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>110531</v>
+        <v>108657</v>
       </c>
       <c r="I11" t="n">
         <v>1.66</v>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>28.95</v>
+        <v>29.41</v>
       </c>
       <c r="D12" t="n">
         <v>26.09</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>76149</v>
+        <v>80541</v>
       </c>
       <c r="I12" t="n">
         <v>1.68</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.38</v>
+        <v>17.07</v>
       </c>
       <c r="D13" t="n">
         <v>14.88</v>
@@ -907,7 +907,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-9.2%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>43209</v>
+        <v>51701</v>
       </c>
       <c r="I13" t="n">
         <v>1.37</v>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>37.11</v>
+        <v>38.29</v>
       </c>
       <c r="D14" t="n">
         <v>57.74</v>
@@ -944,7 +944,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+55.6%</t>
+          <t>+50.8%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.6</v>
+        <v>16.9</v>
       </c>
       <c r="D15" t="n">
         <v>20</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+13.6%</t>
+          <t>+18.3%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>27.15</v>
+        <v>25.81</v>
       </c>
       <c r="D16" t="n">
         <v>26</v>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>+0.7%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>27187</v>
+        <v>21396</v>
       </c>
       <c r="I16" t="n">
         <v>1.23</v>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.69</v>
+        <v>23.68</v>
       </c>
       <c r="D17" t="n">
         <v>25.3</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>16592</v>
+        <v>16540</v>
       </c>
       <c r="I17" t="n">
         <v>1.14</v>
@@ -1082,22 +1082,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>12.79</v>
+        <v>13.24</v>
       </c>
       <c r="D18" t="n">
-        <v>16.71</v>
+        <v>15.24</v>
       </c>
       <c r="E18" t="n">
         <v>18.9</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+30.7%</t>
+          <t>+15.1%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-19.3%</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1119,26 +1119,26 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.78</v>
+        <v>2.54</v>
       </c>
       <c r="D19" t="n">
-        <v>2.13</v>
+        <v>1.99</v>
       </c>
       <c r="E19" t="n">
         <v>2.63</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-23.4%</t>
+          <t>-21.5%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-19.0%</t>
+          <t>-24.2%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>350590</v>
+        <v>299648</v>
       </c>
       <c r="I19" t="n">
         <v>1.21</v>
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>38.99</v>
+        <v>37.89</v>
       </c>
       <c r="D20" t="n">
         <v>33.61</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-13.8%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1179,6 +1179,43 @@
       </c>
       <c r="I20" t="n">
         <v>1.45</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>BRUT</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D21" t="n">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="E21" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>+81.3%</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>+37.3%</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.79</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -1085,14 +1085,14 @@
         <v>13.24</v>
       </c>
       <c r="D18" t="n">
-        <v>15.24</v>
+        <v>15.25</v>
       </c>
       <c r="E18" t="n">
         <v>18.9</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+15.1%</t>
+          <t>+15.2%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -493,23 +493,23 @@
         <v>18.89</v>
       </c>
       <c r="D2" t="n">
-        <v>14.31</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
         <v>16</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-24.3%</t>
+          <t>-25.9%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>506266</v>
+        <v>529540</v>
       </c>
       <c r="I2" t="n">
         <v>2.79</v>
@@ -530,23 +530,23 @@
         <v>52.48</v>
       </c>
       <c r="D3" t="n">
-        <v>36.67</v>
+        <v>36.6</v>
       </c>
       <c r="E3" t="n">
         <v>45</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-30.1%</t>
+          <t>-30.3%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-18.5%</t>
+          <t>-18.7%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>377597</v>
+        <v>343849</v>
       </c>
       <c r="I3" t="n">
         <v>2.5</v>
@@ -567,23 +567,23 @@
         <v>40.93</v>
       </c>
       <c r="D4" t="n">
-        <v>26.93</v>
+        <v>26.4</v>
       </c>
       <c r="E4" t="n">
         <v>30.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-34.2%</t>
+          <t>-35.5%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-13.4%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>472015</v>
+        <v>469143</v>
       </c>
       <c r="I4" t="n">
         <v>2.57</v>
@@ -604,23 +604,23 @@
         <v>55.1691215792289</v>
       </c>
       <c r="D5" t="n">
-        <v>37.31</v>
+        <v>38.45</v>
       </c>
       <c r="E5" t="n">
         <v>51.91081980765414</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-32.4%</t>
+          <t>-30.3%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-28.1%</t>
+          <t>-25.9%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>414323</v>
+        <v>316872</v>
       </c>
       <c r="I5" t="n">
         <v>2.4</v>
@@ -641,23 +641,23 @@
         <v>74.45</v>
       </c>
       <c r="D6" t="n">
-        <v>73.94</v>
+        <v>79.39</v>
       </c>
       <c r="E6" t="n">
         <v>75</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>+6.6%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>+5.9%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>100249</v>
+        <v>41889</v>
       </c>
       <c r="I6" t="n">
         <v>2.15</v>
@@ -678,23 +678,23 @@
         <v>5.85</v>
       </c>
       <c r="D7" t="n">
-        <v>2.59</v>
+        <v>2.51</v>
       </c>
       <c r="E7" t="n">
         <v>6</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-55.7%</t>
+          <t>-57.0%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-56.8%</t>
+          <t>-58.1%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>396401</v>
+        <v>404139</v>
       </c>
       <c r="I7" t="n">
         <v>2.21</v>
@@ -715,23 +715,23 @@
         <v>29.74</v>
       </c>
       <c r="D8" t="n">
-        <v>26.27</v>
+        <v>28.16</v>
       </c>
       <c r="E8" t="n">
         <v>25</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+5.1%</t>
+          <t>+12.7%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3162500</v>
+        <v>148289</v>
       </c>
       <c r="I8" t="n">
         <v>0.71</v>
@@ -752,19 +752,19 @@
         <v>20.03</v>
       </c>
       <c r="D9" t="n">
-        <v>22.88</v>
+        <v>32.08</v>
       </c>
       <c r="E9" t="n">
         <v>25.17</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+14.2%</t>
+          <t>+60.2%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>+27.5%</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -789,23 +789,23 @@
         <v>80.58</v>
       </c>
       <c r="D10" t="n">
-        <v>74</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="E10" t="n">
         <v>94</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-21.3%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2725019</v>
+        <v>62640</v>
       </c>
       <c r="I10" t="n">
         <v>1.75</v>
@@ -826,23 +826,23 @@
         <v>7.23</v>
       </c>
       <c r="D11" t="n">
-        <v>5.59</v>
+        <v>5.66</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-22.7%</t>
+          <t>-21.7%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-44.1%</t>
+          <t>-43.4%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>108657</v>
+        <v>95336</v>
       </c>
       <c r="I11" t="n">
         <v>1.66</v>
@@ -863,23 +863,23 @@
         <v>29.41</v>
       </c>
       <c r="D12" t="n">
-        <v>26.09</v>
+        <v>26.35</v>
       </c>
       <c r="E12" t="n">
         <v>25</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-10.4%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+4.4%</t>
+          <t>+5.4%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>80541</v>
+        <v>71405</v>
       </c>
       <c r="I12" t="n">
         <v>1.68</v>
@@ -900,23 +900,23 @@
         <v>17.07</v>
       </c>
       <c r="D13" t="n">
-        <v>14.88</v>
+        <v>15.09</v>
       </c>
       <c r="E13" t="n">
         <v>17.95</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>51701</v>
+        <v>41676</v>
       </c>
       <c r="I13" t="n">
         <v>1.37</v>
@@ -937,19 +937,19 @@
         <v>38.29</v>
       </c>
       <c r="D14" t="n">
-        <v>57.74</v>
+        <v>60.66</v>
       </c>
       <c r="E14" t="n">
         <v>51.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+50.8%</t>
+          <t>+58.4%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+12.1%</t>
+          <t>+17.8%</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -974,19 +974,19 @@
         <v>16.9</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>21.12</v>
       </c>
       <c r="E15" t="n">
         <v>27.98</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+18.3%</t>
+          <t>+25.0%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-28.5%</t>
+          <t>-24.5%</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1011,23 +1011,23 @@
         <v>25.81</v>
       </c>
       <c r="D16" t="n">
-        <v>26</v>
+        <v>25.68</v>
       </c>
       <c r="E16" t="n">
         <v>34.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+0.7%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-24.6%</t>
+          <t>-25.6%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>21396</v>
+        <v>22755</v>
       </c>
       <c r="I16" t="n">
         <v>1.23</v>
@@ -1085,23 +1085,23 @@
         <v>13.24</v>
       </c>
       <c r="D18" t="n">
-        <v>15.25</v>
+        <v>15.65</v>
       </c>
       <c r="E18" t="n">
         <v>18.9</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+15.2%</t>
+          <t>+18.2%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-19.3%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2791</v>
       </c>
       <c r="I18" t="n">
         <v>2.5</v>
@@ -1122,23 +1122,23 @@
         <v>2.54</v>
       </c>
       <c r="D19" t="n">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="E19" t="n">
         <v>2.63</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-21.5%</t>
+          <t>-13.8%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-24.2%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>299648</v>
+        <v>137799</v>
       </c>
       <c r="I19" t="n">
         <v>1.21</v>
@@ -1159,23 +1159,23 @@
         <v>37.89</v>
       </c>
       <c r="D20" t="n">
-        <v>33.61</v>
+        <v>43</v>
       </c>
       <c r="E20" t="n">
         <v>52.04</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>+13.5%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-35.4%</t>
+          <t>-17.4%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2757173</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>1.45</v>
@@ -1196,19 +1196,19 @@
         <v>5.4</v>
       </c>
       <c r="D21" t="n">
-        <v>9.789999999999999</v>
+        <v>9.83</v>
       </c>
       <c r="E21" t="n">
         <v>7.13</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+81.3%</t>
+          <t>+82.1%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+37.3%</t>
+          <t>+37.9%</t>
         </is>
       </c>
       <c r="H21" t="n">

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -422,9 +422,9 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="33" customWidth="1" min="8" max="8"/>
@@ -493,23 +493,23 @@
         <v>18.89</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>14.15</v>
       </c>
       <c r="E2" t="n">
         <v>16</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-25.9%</t>
+          <t>-25.1%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>529540</v>
+        <v>518123</v>
       </c>
       <c r="I2" t="n">
         <v>2.79</v>
@@ -530,23 +530,23 @@
         <v>52.48</v>
       </c>
       <c r="D3" t="n">
-        <v>36.6</v>
+        <v>36.78</v>
       </c>
       <c r="E3" t="n">
         <v>45</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-30.3%</t>
+          <t>-29.9%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-18.7%</t>
+          <t>-18.3%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>343849</v>
+        <v>341712</v>
       </c>
       <c r="I3" t="n">
         <v>2.5</v>
@@ -567,23 +567,23 @@
         <v>40.93</v>
       </c>
       <c r="D4" t="n">
-        <v>26.4</v>
+        <v>26.54</v>
       </c>
       <c r="E4" t="n">
         <v>30.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-35.5%</t>
+          <t>-35.2%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-13.4%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>469143</v>
+        <v>466274</v>
       </c>
       <c r="I4" t="n">
         <v>2.57</v>
@@ -601,29 +601,29 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>55.1691215792289</v>
+        <v>55.27902324271707</v>
       </c>
       <c r="D5" t="n">
-        <v>38.45</v>
+        <v>38.63</v>
       </c>
       <c r="E5" t="n">
-        <v>51.91081980765414</v>
+        <v>52.01423065210093</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-30.3%</t>
+          <t>-30.1%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-25.9%</t>
+          <t>-25.7%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>316872</v>
+        <v>316781</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="6">
@@ -641,14 +641,14 @@
         <v>74.45</v>
       </c>
       <c r="D6" t="n">
-        <v>79.39</v>
+        <v>79.42</v>
       </c>
       <c r="E6" t="n">
         <v>75</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+6.6%</t>
+          <t>+6.7%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -657,10 +657,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>41889</v>
+        <v>41652</v>
       </c>
       <c r="I6" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="7">
@@ -937,26 +937,26 @@
         <v>38.29</v>
       </c>
       <c r="D14" t="n">
-        <v>60.66</v>
+        <v>60.74</v>
       </c>
       <c r="E14" t="n">
         <v>51.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+58.4%</t>
+          <t>+58.6%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+17.8%</t>
+          <t>+18.0%</t>
         </is>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1.97</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="15">
@@ -1085,7 +1085,7 @@
         <v>13.24</v>
       </c>
       <c r="D18" t="n">
-        <v>15.65</v>
+        <v>15.66</v>
       </c>
       <c r="E18" t="n">
         <v>18.9</v>
@@ -1101,10 +1101,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2791</v>
+        <v>2701</v>
       </c>
       <c r="I18" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="19">
@@ -1196,7 +1196,7 @@
         <v>5.4</v>
       </c>
       <c r="D21" t="n">
-        <v>9.83</v>
+        <v>9.84</v>
       </c>
       <c r="E21" t="n">
         <v>7.13</v>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18.89</v>
+        <v>17.65</v>
       </c>
       <c r="D2" t="n">
         <v>14.15</v>
@@ -500,7 +500,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-25.1%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>518123</v>
+        <v>423096</v>
       </c>
       <c r="I2" t="n">
         <v>2.79</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>52.48</v>
+        <v>49.88</v>
       </c>
       <c r="D3" t="n">
         <v>36.78</v>
@@ -537,7 +537,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-29.9%</t>
+          <t>-26.3%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>341712</v>
+        <v>304990</v>
       </c>
       <c r="I3" t="n">
         <v>2.5</v>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>40.93</v>
+        <v>35.52</v>
       </c>
       <c r="D4" t="n">
         <v>26.54</v>
@@ -574,7 +574,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-35.2%</t>
+          <t>-25.3%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>466274</v>
+        <v>339908</v>
       </c>
       <c r="I4" t="n">
         <v>2.57</v>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>55.27902324271707</v>
+        <v>52.02077332262321</v>
       </c>
       <c r="D5" t="n">
         <v>38.63</v>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-30.1%</t>
+          <t>-25.7%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>316781</v>
+        <v>276426</v>
       </c>
       <c r="I5" t="n">
         <v>2.35</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>74.45</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="D6" t="n">
         <v>79.42</v>
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+6.7%</t>
+          <t>+16.8%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>41652</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>1.9</v>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>29.74</v>
+        <v>29.48</v>
       </c>
       <c r="D8" t="n">
         <v>28.16</v>
@@ -722,7 +722,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>148289</v>
+        <v>134259</v>
       </c>
       <c r="I8" t="n">
         <v>0.71</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20.03</v>
+        <v>20.71</v>
       </c>
       <c r="D9" t="n">
         <v>32.08</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+60.2%</t>
+          <t>+54.9%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>80.58</v>
+        <v>72.58</v>
       </c>
       <c r="D10" t="n">
         <v>78.93000000000001</v>
@@ -796,7 +796,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>+8.8%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>62640</v>
+        <v>23127</v>
       </c>
       <c r="I10" t="n">
         <v>1.75</v>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7.23</v>
+        <v>6.97</v>
       </c>
       <c r="D11" t="n">
         <v>5.66</v>
@@ -833,7 +833,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-21.7%</t>
+          <t>-18.8%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>95336</v>
+        <v>87353</v>
       </c>
       <c r="I11" t="n">
         <v>1.66</v>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29.41</v>
+        <v>26.81</v>
       </c>
       <c r="D12" t="n">
         <v>26.35</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-10.4%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>71405</v>
+        <v>52226</v>
       </c>
       <c r="I12" t="n">
         <v>1.68</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.07</v>
+        <v>15.12</v>
       </c>
       <c r="D13" t="n">
         <v>15.09</v>
@@ -907,7 +907,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>41676</v>
+        <v>25023</v>
       </c>
       <c r="I13" t="n">
         <v>1.37</v>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>38.29</v>
+        <v>36.72</v>
       </c>
       <c r="D14" t="n">
         <v>60.74</v>
@@ -944,7 +944,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+58.6%</t>
+          <t>+65.4%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.9</v>
+        <v>17.47</v>
       </c>
       <c r="D15" t="n">
         <v>21.12</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+25.0%</t>
+          <t>+20.9%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>25.81</v>
+        <v>24.4</v>
       </c>
       <c r="D16" t="n">
         <v>25.68</v>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>+5.3%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>22755</v>
+        <v>16931</v>
       </c>
       <c r="I16" t="n">
         <v>1.23</v>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.68</v>
+        <v>23.57</v>
       </c>
       <c r="D17" t="n">
         <v>25.3</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+6.8%</t>
+          <t>+7.3%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>16540</v>
+        <v>15973</v>
       </c>
       <c r="I17" t="n">
         <v>1.14</v>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>13.24</v>
+        <v>12.79</v>
       </c>
       <c r="D18" t="n">
         <v>15.66</v>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+18.2%</t>
+          <t>+22.4%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2701</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>2.46</v>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.54</v>
+        <v>2.61</v>
       </c>
       <c r="D19" t="n">
         <v>2.19</v>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-13.8%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>137799</v>
+        <v>155119</v>
       </c>
       <c r="I19" t="n">
         <v>1.21</v>
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>37.89</v>
+        <v>37.79</v>
       </c>
       <c r="D20" t="n">
         <v>43</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+13.5%</t>
+          <t>+13.8%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5.4</v>
+        <v>5.34</v>
       </c>
       <c r="D21" t="n">
         <v>9.84</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+82.1%</t>
+          <t>+84.2%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1216,6 +1216,43 @@
       </c>
       <c r="I21" t="n">
         <v>2.79</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CMBT</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>14.69</v>
+      </c>
+      <c r="E22" t="n">
+        <v>16.59</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>+4.1%</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-11.5%</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>38245</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -974,23 +974,23 @@
         <v>17.47</v>
       </c>
       <c r="D15" t="n">
-        <v>21.12</v>
+        <v>20.43</v>
       </c>
       <c r="E15" t="n">
         <v>27.98</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+20.9%</t>
+          <t>+16.9%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-24.5%</t>
+          <t>-27.0%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2713</v>
       </c>
       <c r="I15" t="n">
         <v>1.21</v>
@@ -1011,23 +1011,23 @@
         <v>24.4</v>
       </c>
       <c r="D16" t="n">
-        <v>25.68</v>
+        <v>26</v>
       </c>
       <c r="E16" t="n">
         <v>34.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+5.3%</t>
+          <t>+6.6%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-25.6%</t>
+          <t>-24.6%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>16931</v>
+        <v>15583</v>
       </c>
       <c r="I16" t="n">
         <v>1.23</v>
@@ -1048,23 +1048,23 @@
         <v>23.57</v>
       </c>
       <c r="D17" t="n">
-        <v>25.3</v>
+        <v>23.96</v>
       </c>
       <c r="E17" t="n">
         <v>24.8</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+7.3%</t>
+          <t>+1.7%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+2.0%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>15973</v>
+        <v>22647</v>
       </c>
       <c r="I17" t="n">
         <v>1.14</v>
@@ -1233,7 +1233,7 @@
         <v>14.1</v>
       </c>
       <c r="D22" t="n">
-        <v>14.69</v>
+        <v>14.68</v>
       </c>
       <c r="E22" t="n">
         <v>16.59</v>
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>38245</v>
+        <v>38337</v>
       </c>
       <c r="I22" t="n">
         <v>1.5</v>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1255,6 +1255,43 @@
         <v>1.5</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="D23" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="E23" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>+52.0%</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>+36.8%</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -1270,26 +1270,26 @@
         <v>6.39</v>
       </c>
       <c r="D23" t="n">
-        <v>9.710000000000001</v>
+        <v>9.48</v>
       </c>
       <c r="E23" t="n">
         <v>7.1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+52.0%</t>
+          <t>+48.4%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+36.8%</t>
+          <t>+33.5%</t>
         </is>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -493,23 +493,23 @@
         <v>17.65</v>
       </c>
       <c r="D2" t="n">
-        <v>14.15</v>
+        <v>13.67</v>
       </c>
       <c r="E2" t="n">
         <v>16</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-22.5%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-14.5%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>423096</v>
+        <v>459855</v>
       </c>
       <c r="I2" t="n">
         <v>2.79</v>
@@ -530,23 +530,23 @@
         <v>49.88</v>
       </c>
       <c r="D3" t="n">
-        <v>36.78</v>
+        <v>35.41</v>
       </c>
       <c r="E3" t="n">
         <v>45</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-26.3%</t>
+          <t>-29.0%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-18.3%</t>
+          <t>-21.3%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>304990</v>
+        <v>326486</v>
       </c>
       <c r="I3" t="n">
         <v>2.5</v>
@@ -567,26 +567,26 @@
         <v>35.52</v>
       </c>
       <c r="D4" t="n">
-        <v>26.54</v>
+        <v>25.28</v>
       </c>
       <c r="E4" t="n">
         <v>30.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-25.3%</t>
+          <t>-28.8%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>339908</v>
+        <v>366009</v>
       </c>
       <c r="I4" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="5">
@@ -937,26 +937,26 @@
         <v>36.72</v>
       </c>
       <c r="D14" t="n">
-        <v>60.74</v>
+        <v>60.34</v>
       </c>
       <c r="E14" t="n">
         <v>51.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+65.4%</t>
+          <t>+64.3%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+18.0%</t>
+          <t>+17.2%</t>
         </is>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="15">
@@ -1048,23 +1048,23 @@
         <v>23.57</v>
       </c>
       <c r="D17" t="n">
-        <v>23.96</v>
+        <v>23.99</v>
       </c>
       <c r="E17" t="n">
         <v>24.8</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+1.7%</t>
+          <t>+1.8%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>22647</v>
+        <v>22511</v>
       </c>
       <c r="I17" t="n">
         <v>1.14</v>
@@ -1085,26 +1085,26 @@
         <v>12.79</v>
       </c>
       <c r="D18" t="n">
-        <v>15.66</v>
+        <v>12.59</v>
       </c>
       <c r="E18" t="n">
         <v>18.9</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+22.4%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-33.4%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>127839</v>
       </c>
       <c r="I18" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="19">
@@ -1196,23 +1196,23 @@
         <v>5.34</v>
       </c>
       <c r="D21" t="n">
-        <v>9.84</v>
+        <v>5.16</v>
       </c>
       <c r="E21" t="n">
         <v>7.13</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+84.2%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+37.9%</t>
+          <t>-27.6%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>181776</v>
       </c>
       <c r="I21" t="n">
         <v>2.79</v>
@@ -1233,26 +1233,26 @@
         <v>14.1</v>
       </c>
       <c r="D22" t="n">
-        <v>14.68</v>
+        <v>14.93</v>
       </c>
       <c r="E22" t="n">
         <v>16.59</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+4.1%</t>
+          <t>+5.9%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-10.0%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>38337</v>
+        <v>36206</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="23">
@@ -1270,26 +1270,26 @@
         <v>6.39</v>
       </c>
       <c r="D23" t="n">
-        <v>9.48</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E23" t="n">
         <v>7.1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+48.4%</t>
+          <t>+53.4%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+33.5%</t>
+          <t>+38.1%</t>
         </is>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -490,26 +490,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.65</v>
+        <v>17.08</v>
       </c>
       <c r="D2" t="n">
-        <v>13.67</v>
+        <v>14.15</v>
       </c>
       <c r="E2" t="n">
         <v>16</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-22.5%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-14.5%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>459855</v>
+        <v>379413</v>
       </c>
       <c r="I2" t="n">
         <v>2.79</v>
@@ -527,29 +527,29 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>49.88</v>
+        <v>49.6</v>
       </c>
       <c r="D3" t="n">
-        <v>35.41</v>
+        <v>37.33</v>
       </c>
       <c r="E3" t="n">
         <v>45</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-29.0%</t>
+          <t>-24.7%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-21.3%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>326486</v>
+        <v>292039</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="4">
@@ -564,29 +564,29 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>35.52</v>
+        <v>35.44</v>
       </c>
       <c r="D4" t="n">
-        <v>25.28</v>
+        <v>26.54</v>
       </c>
       <c r="E4" t="n">
         <v>30.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-28.8%</t>
+          <t>-25.1%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>366009</v>
+        <v>338039</v>
       </c>
       <c r="I4" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="5">
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>52.02077332262321</v>
+        <v>50.90851933383615</v>
       </c>
       <c r="D5" t="n">
         <v>38.63</v>
@@ -611,16 +611,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>-24.1%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>-25.7%</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>-25.7%</t>
-        </is>
-      </c>
       <c r="H5" t="n">
-        <v>276426</v>
+        <v>262650</v>
       </c>
       <c r="I5" t="n">
         <v>2.35</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>67.98999999999999</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="D6" t="n">
         <v>79.42</v>
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+16.8%</t>
+          <t>+20.4%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5.85</v>
+        <v>5.78</v>
       </c>
       <c r="D7" t="n">
         <v>2.51</v>
@@ -685,7 +685,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-57.0%</t>
+          <t>-56.5%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>404139</v>
+        <v>397445</v>
       </c>
       <c r="I7" t="n">
         <v>2.21</v>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>29.48</v>
+        <v>29.29</v>
       </c>
       <c r="D8" t="n">
         <v>28.16</v>
@@ -722,7 +722,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>134259</v>
+        <v>124006</v>
       </c>
       <c r="I8" t="n">
         <v>0.71</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20.71</v>
+        <v>20.87</v>
       </c>
       <c r="D9" t="n">
         <v>32.08</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+54.9%</t>
+          <t>+53.7%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>72.58</v>
+        <v>70.09</v>
       </c>
       <c r="D10" t="n">
         <v>78.93000000000001</v>
@@ -796,7 +796,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+8.8%</t>
+          <t>+12.6%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>23127</v>
+        <v>10829</v>
       </c>
       <c r="I10" t="n">
         <v>1.75</v>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6.97</v>
+        <v>6.86</v>
       </c>
       <c r="D11" t="n">
         <v>5.66</v>
@@ -833,7 +833,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-18.8%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>87353</v>
+        <v>83976</v>
       </c>
       <c r="I11" t="n">
         <v>1.66</v>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>26.81</v>
+        <v>26.31</v>
       </c>
       <c r="D12" t="n">
         <v>26.35</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>+0.2%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>52226</v>
+        <v>48537</v>
       </c>
       <c r="I12" t="n">
         <v>1.68</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>15.12</v>
+        <v>16</v>
       </c>
       <c r="D13" t="n">
         <v>15.09</v>
@@ -907,7 +907,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>25023</v>
+        <v>32539</v>
       </c>
       <c r="I13" t="n">
         <v>1.37</v>
@@ -934,29 +934,29 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>36.72</v>
+        <v>35.76</v>
       </c>
       <c r="D14" t="n">
-        <v>60.34</v>
+        <v>61.29</v>
       </c>
       <c r="E14" t="n">
         <v>51.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+64.3%</t>
+          <t>+71.4%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+17.2%</t>
+          <t>+19.0%</t>
         </is>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="15">
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.47</v>
+        <v>17.99</v>
       </c>
       <c r="D15" t="n">
         <v>20.43</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+16.9%</t>
+          <t>+13.6%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2713</v>
+        <v>5949</v>
       </c>
       <c r="I15" t="n">
         <v>1.21</v>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24.4</v>
+        <v>24.64</v>
       </c>
       <c r="D16" t="n">
         <v>26</v>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+6.6%</t>
+          <t>+5.5%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>15583</v>
+        <v>16572</v>
       </c>
       <c r="I16" t="n">
         <v>1.23</v>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.57</v>
+        <v>24.39</v>
       </c>
       <c r="D17" t="n">
         <v>23.99</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+1.8%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>22511</v>
+        <v>26698</v>
       </c>
       <c r="I17" t="n">
         <v>1.14</v>
@@ -1082,29 +1082,29 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>12.79</v>
+        <v>12.73</v>
       </c>
       <c r="D18" t="n">
-        <v>12.59</v>
+        <v>16.13</v>
       </c>
       <c r="E18" t="n">
         <v>18.9</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>+26.7%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-33.4%</t>
+          <t>-14.7%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>127839</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="19">
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="D19" t="n">
         <v>2.19</v>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>155119</v>
+        <v>157594</v>
       </c>
       <c r="I19" t="n">
         <v>1.21</v>
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>37.79</v>
+        <v>37.74</v>
       </c>
       <c r="D20" t="n">
         <v>43</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+13.8%</t>
+          <t>+13.9%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1193,26 +1193,26 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5.34</v>
+        <v>5.21</v>
       </c>
       <c r="D21" t="n">
-        <v>5.16</v>
+        <v>9.84</v>
       </c>
       <c r="E21" t="n">
         <v>7.13</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>+88.8%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-27.6%</t>
+          <t>+37.9%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>181776</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>2.79</v>
@@ -1230,29 +1230,29 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>14.1</v>
+        <v>14.08</v>
       </c>
       <c r="D22" t="n">
-        <v>14.93</v>
+        <v>15.26</v>
       </c>
       <c r="E22" t="n">
         <v>16.59</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+5.9%</t>
+          <t>+8.4%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-10.0%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>36206</v>
+        <v>32749</v>
       </c>
       <c r="I22" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="23">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6.39</v>
+        <v>6.36</v>
       </c>
       <c r="D23" t="n">
         <v>9.800000000000001</v>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+53.4%</t>
+          <t>+54.1%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -1011,26 +1011,26 @@
         <v>24.64</v>
       </c>
       <c r="D16" t="n">
-        <v>26</v>
+        <v>28.34</v>
       </c>
       <c r="E16" t="n">
         <v>34.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+5.5%</t>
+          <t>+15.0%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-24.6%</t>
+          <t>-17.9%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>16572</v>
+        <v>7455</v>
       </c>
       <c r="I16" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="17">
@@ -1270,26 +1270,26 @@
         <v>6.36</v>
       </c>
       <c r="D23" t="n">
-        <v>9.800000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="E23" t="n">
         <v>7.1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+54.1%</t>
+          <t>+61.9%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+38.1%</t>
+          <t>+45.1%</t>
         </is>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -1270,19 +1270,19 @@
         <v>6.36</v>
       </c>
       <c r="D23" t="n">
-        <v>10.3</v>
+        <v>10.17</v>
       </c>
       <c r="E23" t="n">
         <v>7.1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+61.9%</t>
+          <t>+59.9%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+45.1%</t>
+          <t>+43.2%</t>
         </is>
       </c>
       <c r="H23" t="n">

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -1085,19 +1085,19 @@
         <v>12.73</v>
       </c>
       <c r="D18" t="n">
-        <v>16.13</v>
+        <v>16.03</v>
       </c>
       <c r="E18" t="n">
         <v>18.9</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+26.7%</t>
+          <t>+25.9%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-14.7%</t>
+          <t>-15.2%</t>
         </is>
       </c>
       <c r="H18" t="n">

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -493,23 +493,23 @@
         <v>17.08</v>
       </c>
       <c r="D2" t="n">
-        <v>14.15</v>
+        <v>14.95</v>
       </c>
       <c r="E2" t="n">
         <v>16</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>379413</v>
+        <v>310818</v>
       </c>
       <c r="I2" t="n">
         <v>2.79</v>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.08</v>
+        <v>16.4</v>
       </c>
       <c r="D2" t="n">
         <v>14.95</v>
@@ -500,7 +500,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>310818</v>
+        <v>260972</v>
       </c>
       <c r="I2" t="n">
         <v>2.79</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>49.6</v>
+        <v>50.12</v>
       </c>
       <c r="D3" t="n">
         <v>37.33</v>
@@ -537,7 +537,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-24.7%</t>
+          <t>-25.5%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>292039</v>
+        <v>299354</v>
       </c>
       <c r="I3" t="n">
         <v>2.49</v>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>35.44</v>
+        <v>34.5</v>
       </c>
       <c r="D4" t="n">
         <v>26.54</v>
@@ -574,7 +574,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-25.1%</t>
+          <t>-23.1%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>338039</v>
+        <v>316083</v>
       </c>
       <c r="I4" t="n">
         <v>2.57</v>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50.90851933383615</v>
+        <v>50.11031353011837</v>
       </c>
       <c r="D5" t="n">
         <v>38.63</v>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-24.1%</t>
+          <t>-22.9%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>262650</v>
+        <v>252764</v>
       </c>
       <c r="I5" t="n">
         <v>2.35</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>65.98999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="D6" t="n">
         <v>79.42</v>
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+20.4%</t>
+          <t>+12.2%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>10261</v>
       </c>
       <c r="I6" t="n">
         <v>1.9</v>
@@ -675,26 +675,26 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5.78</v>
+        <v>5.54</v>
       </c>
       <c r="D7" t="n">
-        <v>2.51</v>
+        <v>3.09</v>
       </c>
       <c r="E7" t="n">
         <v>6</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-56.5%</t>
+          <t>-44.2%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-58.1%</t>
+          <t>-48.4%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>397445</v>
+        <v>360646</v>
       </c>
       <c r="I7" t="n">
         <v>2.21</v>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>29.29</v>
+        <v>28.06</v>
       </c>
       <c r="D8" t="n">
         <v>28.16</v>
@@ -722,7 +722,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>+0.4%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>124006</v>
+        <v>57631</v>
       </c>
       <c r="I8" t="n">
         <v>0.71</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20.87</v>
+        <v>21.35</v>
       </c>
       <c r="D9" t="n">
         <v>32.08</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+53.7%</t>
+          <t>+50.3%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>70.09</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="D10" t="n">
         <v>78.93000000000001</v>
@@ -796,7 +796,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+12.6%</t>
+          <t>+4.4%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>10829</v>
+        <v>38043</v>
       </c>
       <c r="I10" t="n">
         <v>1.75</v>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6.86</v>
+        <v>6.64</v>
       </c>
       <c r="D11" t="n">
         <v>5.66</v>
@@ -833,7 +833,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-14.7%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>83976</v>
+        <v>77221</v>
       </c>
       <c r="I11" t="n">
         <v>1.66</v>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>26.31</v>
+        <v>26.06</v>
       </c>
       <c r="D12" t="n">
         <v>26.35</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+0.2%</t>
+          <t>+1.1%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>48537</v>
+        <v>46693</v>
       </c>
       <c r="I12" t="n">
         <v>1.68</v>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>35.76</v>
+        <v>35.37</v>
       </c>
       <c r="D14" t="n">
         <v>61.29</v>
@@ -944,7 +944,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+71.4%</t>
+          <t>+73.3%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.99</v>
+        <v>17.56</v>
       </c>
       <c r="D15" t="n">
         <v>20.43</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+13.6%</t>
+          <t>+16.3%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5949</v>
+        <v>3273</v>
       </c>
       <c r="I15" t="n">
         <v>1.21</v>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24.64</v>
+        <v>24.97</v>
       </c>
       <c r="D16" t="n">
         <v>28.34</v>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+15.0%</t>
+          <t>+13.5%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>7455</v>
+        <v>8819</v>
       </c>
       <c r="I16" t="n">
         <v>1.25</v>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24.39</v>
+        <v>24.78</v>
       </c>
       <c r="D17" t="n">
         <v>23.99</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>26698</v>
+        <v>28690</v>
       </c>
       <c r="I17" t="n">
         <v>1.14</v>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>12.73</v>
+        <v>12.58</v>
       </c>
       <c r="D18" t="n">
         <v>16.03</v>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+25.9%</t>
+          <t>+27.4%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="D19" t="n">
         <v>2.19</v>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-14.1%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>157594</v>
+        <v>140273</v>
       </c>
       <c r="I19" t="n">
         <v>1.21</v>
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>37.74</v>
+        <v>37.6</v>
       </c>
       <c r="D20" t="n">
         <v>43</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+13.9%</t>
+          <t>+14.4%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>14.08</v>
+        <v>13.99</v>
       </c>
       <c r="D22" t="n">
         <v>15.26</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+8.4%</t>
+          <t>+9.1%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>32749</v>
+        <v>31587</v>
       </c>
       <c r="I22" t="n">
         <v>1.5</v>
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6.36</v>
+        <v>6.31</v>
       </c>
       <c r="D23" t="n">
         <v>10.17</v>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+59.9%</t>
+          <t>+61.1%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -900,26 +900,26 @@
         <v>16</v>
       </c>
       <c r="D13" t="n">
-        <v>15.09</v>
+        <v>16.75</v>
       </c>
       <c r="E13" t="n">
         <v>17.95</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>+4.7%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>32539</v>
+        <v>18010</v>
       </c>
       <c r="I13" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="14">
@@ -1270,19 +1270,19 @@
         <v>6.31</v>
       </c>
       <c r="D23" t="n">
-        <v>10.17</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="E23" t="n">
         <v>7.1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+61.1%</t>
+          <t>+56.5%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+43.2%</t>
+          <t>+39.1%</t>
         </is>
       </c>
       <c r="H23" t="n">

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -1196,19 +1196,19 @@
         <v>5.21</v>
       </c>
       <c r="D21" t="n">
-        <v>9.84</v>
+        <v>9.27</v>
       </c>
       <c r="E21" t="n">
         <v>7.13</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+88.8%</t>
+          <t>+77.9%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+37.9%</t>
+          <t>+30.0%</t>
         </is>
       </c>
       <c r="H21" t="n">

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -530,23 +530,23 @@
         <v>50.12</v>
       </c>
       <c r="D3" t="n">
-        <v>37.33</v>
+        <v>37.18</v>
       </c>
       <c r="E3" t="n">
         <v>45</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-25.5%</t>
+          <t>-25.8%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-17.4%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>299354</v>
+        <v>301800</v>
       </c>
       <c r="I3" t="n">
         <v>2.49</v>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -826,23 +826,23 @@
         <v>6.64</v>
       </c>
       <c r="D11" t="n">
-        <v>5.66</v>
+        <v>5.99</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-14.7%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-43.4%</t>
+          <t>-40.1%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>77221</v>
+        <v>67495</v>
       </c>
       <c r="I11" t="n">
         <v>1.66</v>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -789,26 +789,26 @@
         <v>75.59999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>78.93000000000001</v>
+        <v>76.13</v>
       </c>
       <c r="E10" t="n">
         <v>94</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+4.4%</t>
+          <t>+0.7%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-19.0%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>38043</v>
+        <v>53301</v>
       </c>
       <c r="I10" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="11">

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -863,26 +863,26 @@
         <v>26.06</v>
       </c>
       <c r="D12" t="n">
-        <v>26.35</v>
+        <v>30.97</v>
       </c>
       <c r="E12" t="n">
         <v>25</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+1.1%</t>
+          <t>+18.8%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+5.4%</t>
+          <t>+23.9%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>46693</v>
+        <v>12733</v>
       </c>
       <c r="I12" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="13">

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.4</v>
+        <v>16.53</v>
       </c>
       <c r="D2" t="n">
         <v>14.95</v>
@@ -500,7 +500,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>260972</v>
+        <v>270502</v>
       </c>
       <c r="I2" t="n">
         <v>2.79</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>50.12</v>
+        <v>49.94</v>
       </c>
       <c r="D3" t="n">
         <v>37.18</v>
@@ -537,7 +537,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-25.8%</t>
+          <t>-25.5%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>301800</v>
+        <v>299265</v>
       </c>
       <c r="I3" t="n">
         <v>2.49</v>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>34.5</v>
+        <v>34.7</v>
       </c>
       <c r="D4" t="n">
         <v>26.54</v>
@@ -574,7 +574,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-23.1%</t>
+          <t>-23.5%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>316083</v>
+        <v>320754</v>
       </c>
       <c r="I4" t="n">
         <v>2.57</v>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50.11031353011837</v>
+        <v>50.88889132226932</v>
       </c>
       <c r="D5" t="n">
         <v>38.63</v>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-22.9%</t>
+          <t>-24.1%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>252764</v>
+        <v>262407</v>
       </c>
       <c r="I5" t="n">
         <v>2.35</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>70.8</v>
+        <v>64.33</v>
       </c>
       <c r="D6" t="n">
         <v>79.42</v>
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+12.2%</t>
+          <t>+23.5%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>10261</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>1.9</v>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5.54</v>
+        <v>5.56</v>
       </c>
       <c r="D7" t="n">
         <v>3.09</v>
@@ -685,7 +685,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-44.2%</t>
+          <t>-44.4%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>360646</v>
+        <v>362899</v>
       </c>
       <c r="I7" t="n">
         <v>2.21</v>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>28.06</v>
+        <v>28.62</v>
       </c>
       <c r="D8" t="n">
         <v>28.16</v>
@@ -722,7 +722,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+0.4%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>57631</v>
+        <v>87851</v>
       </c>
       <c r="I8" t="n">
         <v>0.71</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.35</v>
+        <v>21.68</v>
       </c>
       <c r="D9" t="n">
         <v>32.08</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+50.3%</t>
+          <t>+48.0%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>75.59999999999999</v>
+        <v>69.53</v>
       </c>
       <c r="D10" t="n">
         <v>76.13</v>
@@ -796,7 +796,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+0.7%</t>
+          <t>+9.5%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>53301</v>
+        <v>21075</v>
       </c>
       <c r="I10" t="n">
         <v>1.77</v>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6.64</v>
+        <v>6.56</v>
       </c>
       <c r="D11" t="n">
         <v>5.99</v>
@@ -833,7 +833,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-9.8%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>67495</v>
+        <v>65013</v>
       </c>
       <c r="I11" t="n">
         <v>1.66</v>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>26.06</v>
+        <v>26.25</v>
       </c>
       <c r="D12" t="n">
         <v>30.97</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+18.8%</t>
+          <t>+18.0%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>12733</v>
+        <v>14186</v>
       </c>
       <c r="I12" t="n">
         <v>1.67</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16</v>
+        <v>14.25</v>
       </c>
       <c r="D13" t="n">
         <v>16.75</v>
@@ -907,7 +907,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+4.7%</t>
+          <t>+17.6%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>18010</v>
+        <v>1481</v>
       </c>
       <c r="I13" t="n">
         <v>1.38</v>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.56</v>
+        <v>18.21</v>
       </c>
       <c r="D15" t="n">
         <v>20.43</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+16.3%</t>
+          <t>+12.2%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>3273</v>
+        <v>7318</v>
       </c>
       <c r="I15" t="n">
         <v>1.21</v>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24.97</v>
+        <v>24.81</v>
       </c>
       <c r="D16" t="n">
         <v>28.34</v>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+13.5%</t>
+          <t>+14.2%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>8819</v>
+        <v>8164</v>
       </c>
       <c r="I16" t="n">
         <v>1.25</v>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24.78</v>
+        <v>24.66</v>
       </c>
       <c r="D17" t="n">
         <v>23.99</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>28690</v>
+        <v>28077</v>
       </c>
       <c r="I17" t="n">
         <v>1.14</v>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>12.58</v>
+        <v>12.49</v>
       </c>
       <c r="D18" t="n">
         <v>16.03</v>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+27.4%</t>
+          <t>+28.3%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="D19" t="n">
         <v>2.19</v>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-14.1%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>140273</v>
+        <v>108107</v>
       </c>
       <c r="I19" t="n">
         <v>1.21</v>
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>37.6</v>
+        <v>37.78</v>
       </c>
       <c r="D20" t="n">
         <v>43</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+14.4%</t>
+          <t>+13.8%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5.21</v>
+        <v>5.17</v>
       </c>
       <c r="D21" t="n">
         <v>9.27</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+77.9%</t>
+          <t>+79.3%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>13.99</v>
+        <v>14.05</v>
       </c>
       <c r="D22" t="n">
         <v>15.26</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+9.1%</t>
+          <t>+8.6%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>31587</v>
+        <v>32362</v>
       </c>
       <c r="I22" t="n">
         <v>1.5</v>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -990,10 +990,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>7318</v>
+        <v>7396</v>
       </c>
       <c r="I15" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="16">
@@ -1011,14 +1011,14 @@
         <v>24.81</v>
       </c>
       <c r="D16" t="n">
-        <v>28.34</v>
+        <v>28.32</v>
       </c>
       <c r="E16" t="n">
         <v>34.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+14.2%</t>
+          <t>+14.1%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1027,10 +1027,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>8164</v>
+        <v>8259</v>
       </c>
       <c r="I16" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="17">
@@ -1048,26 +1048,26 @@
         <v>24.66</v>
       </c>
       <c r="D17" t="n">
-        <v>23.99</v>
+        <v>23.85</v>
       </c>
       <c r="E17" t="n">
         <v>24.8</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>28077</v>
+        <v>30712</v>
       </c>
       <c r="I17" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="18">
@@ -1233,26 +1233,26 @@
         <v>14.05</v>
       </c>
       <c r="D22" t="n">
-        <v>15.26</v>
+        <v>15.19</v>
       </c>
       <c r="E22" t="n">
         <v>16.59</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+8.6%</t>
+          <t>+8.1%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>32362</v>
+        <v>29270</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="23">
@@ -1270,26 +1270,26 @@
         <v>6.31</v>
       </c>
       <c r="D23" t="n">
-        <v>9.869999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="E23" t="n">
         <v>7.1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+56.5%</t>
+          <t>+54.5%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+39.1%</t>
+          <t>+37.3%</t>
         </is>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.53</v>
+        <v>17.18</v>
       </c>
       <c r="D2" t="n">
         <v>14.95</v>
@@ -500,7 +500,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>270502</v>
+        <v>318149</v>
       </c>
       <c r="I2" t="n">
         <v>2.79</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>49.94</v>
+        <v>53.11</v>
       </c>
       <c r="D3" t="n">
         <v>37.18</v>
@@ -537,7 +537,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-25.5%</t>
+          <t>-30.0%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>299265</v>
+        <v>343913</v>
       </c>
       <c r="I3" t="n">
         <v>2.49</v>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>34.7</v>
+        <v>36.75</v>
       </c>
       <c r="D4" t="n">
         <v>26.54</v>
@@ -574,7 +574,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-27.8%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>320754</v>
+        <v>368638</v>
       </c>
       <c r="I4" t="n">
         <v>2.57</v>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50.88889132226932</v>
+        <v>53.91160510356122</v>
       </c>
       <c r="D5" t="n">
         <v>38.63</v>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-24.1%</t>
+          <t>-28.3%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>262407</v>
+        <v>299845</v>
       </c>
       <c r="I5" t="n">
         <v>2.35</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>64.33</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D6" t="n">
         <v>79.42</v>
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+23.5%</t>
+          <t>+17.5%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5.56</v>
+        <v>5.81</v>
       </c>
       <c r="D7" t="n">
         <v>3.09</v>
@@ -685,7 +685,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-44.4%</t>
+          <t>-46.8%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>362899</v>
+        <v>391067</v>
       </c>
       <c r="I7" t="n">
         <v>2.21</v>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>28.62</v>
+        <v>29.29</v>
       </c>
       <c r="D8" t="n">
         <v>28.16</v>
@@ -722,7 +722,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>87851</v>
+        <v>124006</v>
       </c>
       <c r="I8" t="n">
         <v>0.71</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.68</v>
+        <v>21.6</v>
       </c>
       <c r="D9" t="n">
         <v>32.08</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+48.0%</t>
+          <t>+48.5%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>69.53</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="D10" t="n">
         <v>76.13</v>
@@ -796,7 +796,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+9.5%</t>
+          <t>+4.3%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>21075</v>
+        <v>39551</v>
       </c>
       <c r="I10" t="n">
         <v>1.77</v>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6.56</v>
+        <v>7.02</v>
       </c>
       <c r="D11" t="n">
         <v>5.99</v>
@@ -833,7 +833,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-14.7%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>65013</v>
+        <v>79286</v>
       </c>
       <c r="I11" t="n">
         <v>1.66</v>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>26.25</v>
+        <v>27.7</v>
       </c>
       <c r="D12" t="n">
         <v>30.97</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+18.0%</t>
+          <t>+11.8%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>14186</v>
+        <v>24799</v>
       </c>
       <c r="I12" t="n">
         <v>1.67</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>14.25</v>
+        <v>14.86</v>
       </c>
       <c r="D13" t="n">
         <v>16.75</v>
@@ -907,7 +907,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+17.6%</t>
+          <t>+12.7%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1481</v>
+        <v>7407</v>
       </c>
       <c r="I13" t="n">
         <v>1.38</v>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>35.37</v>
+        <v>37.37</v>
       </c>
       <c r="D14" t="n">
         <v>61.29</v>
@@ -944,7 +944,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+73.3%</t>
+          <t>+64.0%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>18.21</v>
+        <v>18.18</v>
       </c>
       <c r="D15" t="n">
         <v>20.43</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+12.2%</t>
+          <t>+12.3%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>7396</v>
+        <v>7207</v>
       </c>
       <c r="I15" t="n">
         <v>1.38</v>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24.66</v>
+        <v>24.5</v>
       </c>
       <c r="D17" t="n">
         <v>23.85</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>30712</v>
+        <v>29692</v>
       </c>
       <c r="I17" t="n">
         <v>1.36</v>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>12.49</v>
+        <v>13.28</v>
       </c>
       <c r="D18" t="n">
         <v>16.03</v>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+28.3%</t>
+          <t>+20.7%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="D19" t="n">
         <v>2.19</v>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>108107</v>
+        <v>113055</v>
       </c>
       <c r="I19" t="n">
         <v>1.21</v>
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>37.78</v>
+        <v>38.11</v>
       </c>
       <c r="D20" t="n">
         <v>43</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+13.8%</t>
+          <t>+12.8%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5.17</v>
+        <v>5.29</v>
       </c>
       <c r="D21" t="n">
         <v>9.27</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+79.3%</t>
+          <t>+75.2%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>14.05</v>
+        <v>14.56</v>
       </c>
       <c r="D22" t="n">
         <v>15.19</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+8.1%</t>
+          <t>+4.3%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>29270</v>
+        <v>38015</v>
       </c>
       <c r="I22" t="n">
         <v>1.66</v>
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6.31</v>
+        <v>6.4</v>
       </c>
       <c r="D23" t="n">
         <v>9.75</v>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+54.5%</t>
+          <t>+52.4%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24.81</v>
+        <v>25.15</v>
       </c>
       <c r="D16" t="n">
         <v>28.32</v>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+14.1%</t>
+          <t>+12.6%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>8259</v>
+        <v>9650</v>
       </c>
       <c r="I16" t="n">
         <v>1.42</v>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>13.28</v>
+        <v>13.68</v>
       </c>
       <c r="D18" t="n">
         <v>16.03</v>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+20.7%</t>
+          <t>+17.2%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>6063</v>
       </c>
       <c r="I18" t="n">
         <v>2.46</v>
@@ -1119,29 +1119,29 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="D19" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="E19" t="n">
         <v>2.63</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>113055</v>
+        <v>132543</v>
       </c>
       <c r="I19" t="n">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="20">
@@ -1159,26 +1159,26 @@
         <v>38.11</v>
       </c>
       <c r="D20" t="n">
-        <v>43</v>
+        <v>43.06</v>
       </c>
       <c r="E20" t="n">
         <v>52.04</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+12.8%</t>
+          <t>+13.0%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-17.4%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="21">
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5.29</v>
+        <v>5.32</v>
       </c>
       <c r="D21" t="n">
         <v>9.27</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+75.2%</t>
+          <t>+74.3%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>38015</v>
+        <v>38026</v>
       </c>
       <c r="I22" t="n">
         <v>1.66</v>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.18</v>
+        <v>16.93</v>
       </c>
       <c r="D2" t="n">
         <v>14.95</v>
@@ -500,7 +500,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>318149</v>
+        <v>299823</v>
       </c>
       <c r="I2" t="n">
         <v>2.79</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>53.11</v>
+        <v>52.23</v>
       </c>
       <c r="D3" t="n">
         <v>37.18</v>
@@ -537,7 +537,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-30.0%</t>
+          <t>-28.8%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>343913</v>
+        <v>331519</v>
       </c>
       <c r="I3" t="n">
         <v>2.49</v>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>36.75</v>
+        <v>36.56</v>
       </c>
       <c r="D4" t="n">
         <v>26.54</v>
@@ -574,7 +574,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-27.8%</t>
+          <t>-27.4%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>368638</v>
+        <v>364200</v>
       </c>
       <c r="I4" t="n">
         <v>2.57</v>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>53.91160510356122</v>
+        <v>54.29107999385327</v>
       </c>
       <c r="D5" t="n">
         <v>38.63</v>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-28.3%</t>
+          <t>-28.9%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>299845</v>
+        <v>304545</v>
       </c>
       <c r="I5" t="n">
         <v>2.35</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>67.59999999999999</v>
+        <v>69.27</v>
       </c>
       <c r="D6" t="n">
         <v>79.42</v>
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+17.5%</t>
+          <t>+14.7%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5.81</v>
+        <v>5.9</v>
       </c>
       <c r="D7" t="n">
         <v>3.09</v>
@@ -685,7 +685,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-46.8%</t>
+          <t>-47.6%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>391067</v>
+        <v>401208</v>
       </c>
       <c r="I7" t="n">
         <v>2.21</v>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>29.29</v>
+        <v>29.17</v>
       </c>
       <c r="D8" t="n">
         <v>28.16</v>
@@ -722,7 +722,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>124006</v>
+        <v>117530</v>
       </c>
       <c r="I8" t="n">
         <v>0.71</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.6</v>
+        <v>22.49</v>
       </c>
       <c r="D9" t="n">
         <v>32.08</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+48.5%</t>
+          <t>+42.7%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>73.01000000000001</v>
+        <v>76.25</v>
       </c>
       <c r="D10" t="n">
         <v>76.13</v>
@@ -796,7 +796,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+4.3%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>39551</v>
+        <v>56752</v>
       </c>
       <c r="I10" t="n">
         <v>1.77</v>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>27.7</v>
+        <v>28.06</v>
       </c>
       <c r="D12" t="n">
         <v>30.97</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+11.8%</t>
+          <t>+10.4%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>24799</v>
+        <v>27403</v>
       </c>
       <c r="I12" t="n">
         <v>1.67</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>14.86</v>
+        <v>15.32</v>
       </c>
       <c r="D13" t="n">
         <v>16.75</v>
@@ -907,7 +907,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+12.7%</t>
+          <t>+9.3%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>7407</v>
+        <v>11815</v>
       </c>
       <c r="I13" t="n">
         <v>1.38</v>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>37.37</v>
+        <v>38.22</v>
       </c>
       <c r="D14" t="n">
         <v>61.29</v>
@@ -944,7 +944,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+64.0%</t>
+          <t>+60.4%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>18.18</v>
+        <v>19.08</v>
       </c>
       <c r="D15" t="n">
         <v>20.43</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+12.3%</t>
+          <t>+7.0%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>7207</v>
+        <v>12866</v>
       </c>
       <c r="I15" t="n">
         <v>1.38</v>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>25.15</v>
+        <v>25.88</v>
       </c>
       <c r="D16" t="n">
         <v>28.32</v>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+12.6%</t>
+          <t>+9.4%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>9650</v>
+        <v>12503</v>
       </c>
       <c r="I16" t="n">
         <v>1.42</v>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24.5</v>
+        <v>24.31</v>
       </c>
       <c r="D17" t="n">
         <v>23.85</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>29692</v>
+        <v>28480</v>
       </c>
       <c r="I17" t="n">
         <v>1.36</v>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>13.68</v>
+        <v>13.06</v>
       </c>
       <c r="D18" t="n">
         <v>16.03</v>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+17.2%</t>
+          <t>+22.7%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>6063</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>2.46</v>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="D19" t="n">
         <v>2.21</v>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>132543</v>
+        <v>124928</v>
       </c>
       <c r="I19" t="n">
         <v>1.31</v>
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>38.11</v>
+        <v>39.44</v>
       </c>
       <c r="D20" t="n">
         <v>43.06</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+13.0%</t>
+          <t>+9.2%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>4829</v>
       </c>
       <c r="I20" t="n">
         <v>1.49</v>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5.32</v>
+        <v>5.66</v>
       </c>
       <c r="D21" t="n">
         <v>9.27</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+74.3%</t>
+          <t>+63.8%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>14.56</v>
+        <v>14.93</v>
       </c>
       <c r="D22" t="n">
         <v>15.19</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+4.3%</t>
+          <t>+1.7%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>38026</v>
+        <v>44372</v>
       </c>
       <c r="I22" t="n">
         <v>1.66</v>
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="D23" t="n">
         <v>9.75</v>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+52.4%</t>
+          <t>+45.5%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1290,6 +1290,80 @@
       </c>
       <c r="I23" t="n">
         <v>1.53</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>LPG</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>36</v>
+      </c>
+      <c r="D24" t="n">
+        <v>32.76</v>
+      </c>
+      <c r="E24" t="n">
+        <v>54</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-9.0%</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-39.3%</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>90798</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>BWLP</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="D25" t="n">
+        <v>15.43</v>
+      </c>
+      <c r="E25" t="n">
+        <v>17.52</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-16.7%</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-11.9%</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>124605</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.59</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.93</v>
+        <v>17.76</v>
       </c>
       <c r="D2" t="n">
         <v>14.95</v>
@@ -500,7 +500,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>299823</v>
+        <v>360665</v>
       </c>
       <c r="I2" t="n">
         <v>2.79</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>52.23</v>
+        <v>54.94</v>
       </c>
       <c r="D3" t="n">
         <v>37.18</v>
@@ -537,7 +537,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-28.8%</t>
+          <t>-32.3%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>331519</v>
+        <v>369687</v>
       </c>
       <c r="I3" t="n">
         <v>2.49</v>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>36.56</v>
+        <v>38.13</v>
       </c>
       <c r="D4" t="n">
         <v>26.54</v>
@@ -574,7 +574,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-30.4%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>364200</v>
+        <v>400872</v>
       </c>
       <c r="I4" t="n">
         <v>2.57</v>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>54.29107999385327</v>
+        <v>57.88954878110554</v>
       </c>
       <c r="D5" t="n">
         <v>38.63</v>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-28.9%</t>
+          <t>-33.3%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>304545</v>
+        <v>349114</v>
       </c>
       <c r="I5" t="n">
         <v>2.35</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>69.27</v>
+        <v>72.45</v>
       </c>
       <c r="D6" t="n">
         <v>79.42</v>
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+14.7%</t>
+          <t>+9.6%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>24452</v>
       </c>
       <c r="I6" t="n">
         <v>1.9</v>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5.9</v>
+        <v>6.17</v>
       </c>
       <c r="D7" t="n">
         <v>3.09</v>
@@ -685,7 +685,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-47.6%</t>
+          <t>-49.9%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>401208</v>
+        <v>431629</v>
       </c>
       <c r="I7" t="n">
         <v>2.21</v>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>29.17</v>
+        <v>30.01</v>
       </c>
       <c r="D8" t="n">
         <v>28.16</v>
@@ -722,7 +722,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>117530</v>
+        <v>162859</v>
       </c>
       <c r="I8" t="n">
         <v>0.71</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.49</v>
+        <v>22.31</v>
       </c>
       <c r="D9" t="n">
         <v>32.08</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+42.7%</t>
+          <t>+43.8%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>76.25</v>
+        <v>79.31999999999999</v>
       </c>
       <c r="D10" t="n">
         <v>76.13</v>
@@ -796,7 +796,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>56752</v>
+        <v>73052</v>
       </c>
       <c r="I10" t="n">
         <v>1.77</v>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7.02</v>
+        <v>7.27</v>
       </c>
       <c r="D11" t="n">
         <v>5.99</v>
@@ -833,7 +833,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-14.7%</t>
+          <t>-17.7%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>79286</v>
+        <v>87044</v>
       </c>
       <c r="I11" t="n">
         <v>1.66</v>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>28.06</v>
+        <v>29.48</v>
       </c>
       <c r="D12" t="n">
         <v>30.97</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+10.4%</t>
+          <t>+5.1%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>27403</v>
+        <v>37673</v>
       </c>
       <c r="I12" t="n">
         <v>1.67</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>15.32</v>
+        <v>16.39</v>
       </c>
       <c r="D13" t="n">
         <v>16.75</v>
@@ -907,7 +907,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+9.3%</t>
+          <t>+2.2%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>11815</v>
+        <v>21504</v>
       </c>
       <c r="I13" t="n">
         <v>1.38</v>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>38.22</v>
+        <v>39.66</v>
       </c>
       <c r="D14" t="n">
         <v>61.29</v>
@@ -944,7 +944,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+60.4%</t>
+          <t>+54.5%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>19.08</v>
+        <v>19.07</v>
       </c>
       <c r="D15" t="n">
         <v>20.43</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+7.0%</t>
+          <t>+7.1%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>12866</v>
+        <v>12804</v>
       </c>
       <c r="I15" t="n">
         <v>1.38</v>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>25.88</v>
+        <v>26.35</v>
       </c>
       <c r="D16" t="n">
         <v>28.32</v>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+9.4%</t>
+          <t>+7.5%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>12503</v>
+        <v>14332</v>
       </c>
       <c r="I16" t="n">
         <v>1.42</v>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24.31</v>
+        <v>25.51</v>
       </c>
       <c r="D17" t="n">
         <v>23.85</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>28480</v>
+        <v>36132</v>
       </c>
       <c r="I17" t="n">
         <v>1.36</v>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>13.06</v>
+        <v>13</v>
       </c>
       <c r="D18" t="n">
         <v>16.03</v>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+22.7%</t>
+          <t>+23.3%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.49</v>
+        <v>2.44</v>
       </c>
       <c r="D19" t="n">
         <v>2.21</v>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>124928</v>
+        <v>112236</v>
       </c>
       <c r="I19" t="n">
         <v>1.31</v>
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>39.44</v>
+        <v>40.06</v>
       </c>
       <c r="D20" t="n">
         <v>43.06</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+9.2%</t>
+          <t>+7.5%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4829</v>
+        <v>19341</v>
       </c>
       <c r="I20" t="n">
         <v>1.49</v>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5.66</v>
+        <v>5.58</v>
       </c>
       <c r="D21" t="n">
         <v>9.27</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+63.8%</t>
+          <t>+66.1%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>14.93</v>
+        <v>15.57</v>
       </c>
       <c r="D22" t="n">
         <v>15.19</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+1.7%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>44372</v>
+        <v>55349</v>
       </c>
       <c r="I22" t="n">
         <v>1.66</v>
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="D23" t="n">
         <v>9.75</v>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+45.5%</t>
+          <t>+41.3%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>36</v>
+        <v>40.05</v>
       </c>
       <c r="D24" t="n">
         <v>32.76</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-18.2%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>90798</v>
+        <v>138721</v>
       </c>
       <c r="I24" t="n">
         <v>1.59</v>
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>18.52</v>
+        <v>19.45</v>
       </c>
       <c r="D25" t="n">
         <v>15.43</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-20.6%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>124605</v>
+        <v>146334</v>
       </c>
       <c r="I25" t="n">
         <v>1.59</v>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -974,26 +974,26 @@
         <v>19.07</v>
       </c>
       <c r="D15" t="n">
-        <v>20.43</v>
+        <v>20.52</v>
       </c>
       <c r="E15" t="n">
         <v>27.98</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+7.1%</t>
+          <t>+7.6%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-27.0%</t>
+          <t>-26.6%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>12804</v>
+        <v>12888</v>
       </c>
       <c r="I15" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="16">
@@ -1011,26 +1011,26 @@
         <v>26.35</v>
       </c>
       <c r="D16" t="n">
-        <v>28.32</v>
+        <v>28.5</v>
       </c>
       <c r="E16" t="n">
         <v>34.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+7.5%</t>
+          <t>+8.1%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-17.9%</t>
+          <t>-17.4%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>14332</v>
+        <v>14427</v>
       </c>
       <c r="I16" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="17">
@@ -1048,26 +1048,26 @@
         <v>25.51</v>
       </c>
       <c r="D17" t="n">
-        <v>23.85</v>
+        <v>23.98</v>
       </c>
       <c r="E17" t="n">
         <v>24.8</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>36132</v>
+        <v>36393</v>
       </c>
       <c r="I17" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="18">
@@ -1233,26 +1233,26 @@
         <v>15.57</v>
       </c>
       <c r="D22" t="n">
-        <v>15.19</v>
+        <v>15.25</v>
       </c>
       <c r="E22" t="n">
         <v>16.59</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>55349</v>
+        <v>55289</v>
       </c>
       <c r="I22" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="23">
@@ -1270,26 +1270,26 @@
         <v>6.9</v>
       </c>
       <c r="D23" t="n">
-        <v>9.75</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="E23" t="n">
         <v>7.1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+41.3%</t>
+          <t>+41.8%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+37.3%</t>
+          <t>+37.8%</t>
         </is>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="24">

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.76</v>
+        <v>17.31</v>
       </c>
       <c r="D2" t="n">
         <v>14.95</v>
@@ -500,7 +500,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-13.6%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>360665</v>
+        <v>327678</v>
       </c>
       <c r="I2" t="n">
         <v>2.79</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>54.94</v>
+        <v>54.2</v>
       </c>
       <c r="D3" t="n">
         <v>37.18</v>
@@ -537,7 +537,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-32.3%</t>
+          <t>-31.4%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>369687</v>
+        <v>359265</v>
       </c>
       <c r="I3" t="n">
         <v>2.49</v>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>38.13</v>
+        <v>36.92</v>
       </c>
       <c r="D4" t="n">
         <v>26.54</v>
@@ -574,7 +574,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-30.4%</t>
+          <t>-28.1%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>400872</v>
+        <v>372609</v>
       </c>
       <c r="I4" t="n">
         <v>2.57</v>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>57.88954878110554</v>
+        <v>56.37819189045959</v>
       </c>
       <c r="D5" t="n">
         <v>38.63</v>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-33.3%</t>
+          <t>-31.5%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>349114</v>
+        <v>330395</v>
       </c>
       <c r="I5" t="n">
         <v>2.35</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>72.45</v>
+        <v>70.72</v>
       </c>
       <c r="D6" t="n">
         <v>79.42</v>
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+9.6%</t>
+          <t>+12.3%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>24452</v>
+        <v>9573</v>
       </c>
       <c r="I6" t="n">
         <v>1.9</v>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6.17</v>
+        <v>6.09</v>
       </c>
       <c r="D7" t="n">
         <v>3.09</v>
@@ -685,7 +685,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-49.9%</t>
+          <t>-49.2%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>431629</v>
+        <v>422616</v>
       </c>
       <c r="I7" t="n">
         <v>2.21</v>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>30.01</v>
+        <v>30.14</v>
       </c>
       <c r="D8" t="n">
         <v>28.16</v>
@@ -722,7 +722,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>162859</v>
+        <v>169874</v>
       </c>
       <c r="I8" t="n">
         <v>0.71</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.31</v>
+        <v>22.38</v>
       </c>
       <c r="D9" t="n">
         <v>32.08</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+43.8%</t>
+          <t>+43.4%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>79.31999999999999</v>
+        <v>77.28</v>
       </c>
       <c r="D10" t="n">
         <v>76.13</v>
@@ -796,7 +796,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>73052</v>
+        <v>62221</v>
       </c>
       <c r="I10" t="n">
         <v>1.77</v>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7.27</v>
+        <v>7.32</v>
       </c>
       <c r="D11" t="n">
         <v>5.99</v>
@@ -833,7 +833,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-17.7%</t>
+          <t>-18.2%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>87044</v>
+        <v>88595</v>
       </c>
       <c r="I11" t="n">
         <v>1.66</v>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29.48</v>
+        <v>28.86</v>
       </c>
       <c r="D12" t="n">
         <v>30.97</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+5.1%</t>
+          <t>+7.3%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>37673</v>
+        <v>33189</v>
       </c>
       <c r="I12" t="n">
         <v>1.67</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.39</v>
+        <v>15.83</v>
       </c>
       <c r="D13" t="n">
         <v>16.75</v>
@@ -907,7 +907,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+2.2%</t>
+          <t>+5.8%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>21504</v>
+        <v>16487</v>
       </c>
       <c r="I13" t="n">
         <v>1.38</v>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>39.66</v>
+        <v>38.83</v>
       </c>
       <c r="D14" t="n">
         <v>61.29</v>
@@ -944,7 +944,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+54.5%</t>
+          <t>+57.8%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>19.07</v>
+        <v>19.56</v>
       </c>
       <c r="D15" t="n">
         <v>20.52</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+7.6%</t>
+          <t>+4.9%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>12888</v>
+        <v>15989</v>
       </c>
       <c r="I15" t="n">
         <v>1.44</v>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>26.35</v>
+        <v>26.54</v>
       </c>
       <c r="D16" t="n">
         <v>28.5</v>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+8.1%</t>
+          <t>+7.4%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>14427</v>
+        <v>15171</v>
       </c>
       <c r="I16" t="n">
         <v>1.49</v>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>25.51</v>
+        <v>25.35</v>
       </c>
       <c r="D17" t="n">
         <v>23.98</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>36393</v>
+        <v>35366</v>
       </c>
       <c r="I17" t="n">
         <v>1.43</v>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>13</v>
+        <v>13.28</v>
       </c>
       <c r="D18" t="n">
         <v>16.03</v>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+23.3%</t>
+          <t>+20.7%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.44</v>
+        <v>2.51</v>
       </c>
       <c r="D19" t="n">
         <v>2.21</v>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>112236</v>
+        <v>130005</v>
       </c>
       <c r="I19" t="n">
         <v>1.31</v>
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>40.06</v>
+        <v>40.81</v>
       </c>
       <c r="D20" t="n">
         <v>43.06</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+7.5%</t>
+          <t>+5.5%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>19341</v>
+        <v>36896</v>
       </c>
       <c r="I20" t="n">
         <v>1.49</v>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5.58</v>
+        <v>5.54</v>
       </c>
       <c r="D21" t="n">
         <v>9.27</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+66.1%</t>
+          <t>+67.3%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>15.57</v>
+        <v>15.44</v>
       </c>
       <c r="D22" t="n">
         <v>15.25</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>55289</v>
+        <v>53061</v>
       </c>
       <c r="I22" t="n">
         <v>1.73</v>
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6.9</v>
+        <v>6.96</v>
       </c>
       <c r="D23" t="n">
         <v>9.779999999999999</v>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+41.8%</t>
+          <t>+40.6%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>40.05</v>
+        <v>40.14</v>
       </c>
       <c r="D24" t="n">
         <v>32.76</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-18.2%</t>
+          <t>-18.4%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>138721</v>
+        <v>139786</v>
       </c>
       <c r="I24" t="n">
         <v>1.59</v>
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>19.45</v>
+        <v>20.1</v>
       </c>
       <c r="D25" t="n">
         <v>15.43</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-20.6%</t>
+          <t>-23.2%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1360,10 +1360,47 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>146334</v>
+        <v>161521</v>
       </c>
       <c r="I25" t="n">
         <v>1.59</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2343</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.443</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-3.8%</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-15.3%</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>18774</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.31</v>
+        <v>18.18</v>
       </c>
       <c r="D2" t="n">
         <v>14.95</v>
@@ -500,7 +500,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-13.6%</t>
+          <t>-17.7%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>327678</v>
+        <v>391452</v>
       </c>
       <c r="I2" t="n">
         <v>2.79</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>54.2</v>
+        <v>56.73</v>
       </c>
       <c r="D3" t="n">
         <v>37.18</v>
@@ -537,7 +537,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-31.4%</t>
+          <t>-34.5%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>359265</v>
+        <v>394899</v>
       </c>
       <c r="I3" t="n">
         <v>2.49</v>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>36.92</v>
+        <v>38.38</v>
       </c>
       <c r="D4" t="n">
         <v>26.54</v>
@@ -574,7 +574,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-28.1%</t>
+          <t>-30.9%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>372609</v>
+        <v>406711</v>
       </c>
       <c r="I4" t="n">
         <v>2.57</v>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>56.37819189045959</v>
+        <v>57.65401264230358</v>
       </c>
       <c r="D5" t="n">
         <v>38.63</v>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-31.5%</t>
+          <t>-33.0%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>330395</v>
+        <v>346197</v>
       </c>
       <c r="I5" t="n">
         <v>2.35</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>70.72</v>
+        <v>72.27</v>
       </c>
       <c r="D6" t="n">
         <v>79.42</v>
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+12.3%</t>
+          <t>+9.9%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>9573</v>
+        <v>22904</v>
       </c>
       <c r="I6" t="n">
         <v>1.9</v>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6.09</v>
+        <v>6.29</v>
       </c>
       <c r="D7" t="n">
         <v>3.09</v>
@@ -685,7 +685,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-49.2%</t>
+          <t>-50.8%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>422616</v>
+        <v>445150</v>
       </c>
       <c r="I7" t="n">
         <v>2.21</v>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>30.14</v>
+        <v>30.81</v>
       </c>
       <c r="D8" t="n">
         <v>28.16</v>
@@ -722,7 +722,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>169874</v>
+        <v>206030</v>
       </c>
       <c r="I8" t="n">
         <v>0.71</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.38</v>
+        <v>22.685</v>
       </c>
       <c r="D9" t="n">
         <v>32.08</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+43.4%</t>
+          <t>+41.4%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>77.28</v>
+        <v>77.87</v>
       </c>
       <c r="D10" t="n">
         <v>76.13</v>
@@ -796,7 +796,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>62221</v>
+        <v>65353</v>
       </c>
       <c r="I10" t="n">
         <v>1.77</v>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7.32</v>
+        <v>7.48</v>
       </c>
       <c r="D11" t="n">
         <v>5.99</v>
@@ -833,7 +833,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-18.2%</t>
+          <t>-20.0%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>88595</v>
+        <v>93560</v>
       </c>
       <c r="I11" t="n">
         <v>1.66</v>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>28.86</v>
+        <v>29.425</v>
       </c>
       <c r="D12" t="n">
         <v>30.97</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+7.3%</t>
+          <t>+5.3%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>33189</v>
+        <v>37275</v>
       </c>
       <c r="I12" t="n">
         <v>1.67</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>15.83</v>
+        <v>16.18</v>
       </c>
       <c r="D13" t="n">
         <v>16.75</v>
@@ -907,7 +907,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+5.8%</t>
+          <t>+3.5%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>16487</v>
+        <v>19623</v>
       </c>
       <c r="I13" t="n">
         <v>1.38</v>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>38.83</v>
+        <v>39.75</v>
       </c>
       <c r="D14" t="n">
         <v>61.29</v>
@@ -944,7 +944,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+57.8%</t>
+          <t>+54.2%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>19.56</v>
+        <v>19.94</v>
       </c>
       <c r="D15" t="n">
         <v>20.52</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+4.9%</t>
+          <t>+2.9%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>15989</v>
+        <v>18395</v>
       </c>
       <c r="I15" t="n">
         <v>1.44</v>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>26.54</v>
+        <v>26.56</v>
       </c>
       <c r="D16" t="n">
         <v>28.5</v>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+7.4%</t>
+          <t>+7.3%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>15171</v>
+        <v>15250</v>
       </c>
       <c r="I16" t="n">
         <v>1.49</v>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>25.35</v>
+        <v>25.45</v>
       </c>
       <c r="D17" t="n">
         <v>23.98</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>35366</v>
+        <v>36008</v>
       </c>
       <c r="I17" t="n">
         <v>1.43</v>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>13.28</v>
+        <v>13.3972</v>
       </c>
       <c r="D18" t="n">
         <v>16.03</v>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+20.7%</t>
+          <t>+19.6%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.51</v>
+        <v>2.5376</v>
       </c>
       <c r="D19" t="n">
         <v>2.21</v>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>130005</v>
+        <v>137011</v>
       </c>
       <c r="I19" t="n">
         <v>1.31</v>
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>40.81</v>
+        <v>41.24</v>
       </c>
       <c r="D20" t="n">
         <v>43.06</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+5.5%</t>
+          <t>+4.4%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>36896</v>
+        <v>46961</v>
       </c>
       <c r="I20" t="n">
         <v>1.49</v>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5.54</v>
+        <v>5.5727</v>
       </c>
       <c r="D21" t="n">
         <v>9.27</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+67.3%</t>
+          <t>+66.4%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>15.44</v>
+        <v>15.78</v>
       </c>
       <c r="D22" t="n">
         <v>15.25</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>53061</v>
+        <v>58887</v>
       </c>
       <c r="I22" t="n">
         <v>1.73</v>
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6.96</v>
+        <v>7.13</v>
       </c>
       <c r="D23" t="n">
         <v>9.779999999999999</v>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+40.6%</t>
+          <t>+37.2%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>40.14</v>
+        <v>41.63</v>
       </c>
       <c r="D24" t="n">
         <v>32.76</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-18.4%</t>
+          <t>-21.3%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>139786</v>
+        <v>157417</v>
       </c>
       <c r="I24" t="n">
         <v>1.59</v>
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>20.1</v>
+        <v>21.1556</v>
       </c>
       <c r="D25" t="n">
         <v>15.43</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-23.2%</t>
+          <t>-27.0%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>161521</v>
+        <v>186184</v>
       </c>
       <c r="I25" t="n">
         <v>1.59</v>
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.39</v>
+        <v>0.3905</v>
       </c>
       <c r="D26" t="n">
         <v>0.38</v>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>18774</v>
+        <v>18872</v>
       </c>
       <c r="I26" t="n">
         <v>1.22</v>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -937,19 +937,19 @@
         <v>39.75</v>
       </c>
       <c r="D14" t="n">
-        <v>61.29</v>
+        <v>61.33</v>
       </c>
       <c r="E14" t="n">
         <v>51.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+54.2%</t>
+          <t>+54.3%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+19.0%</t>
+          <t>+19.1%</t>
         </is>
       </c>
       <c r="H14" t="n">

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -937,26 +937,26 @@
         <v>39.75</v>
       </c>
       <c r="D14" t="n">
-        <v>61.33</v>
+        <v>59.66</v>
       </c>
       <c r="E14" t="n">
         <v>51.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+54.3%</t>
+          <t>+50.1%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+19.1%</t>
+          <t>+15.8%</t>
         </is>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="15">

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18.18</v>
+        <v>17.41</v>
       </c>
       <c r="D2" t="n">
         <v>14.95</v>
@@ -500,7 +500,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-17.7%</t>
+          <t>-14.1%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>391452</v>
+        <v>335008</v>
       </c>
       <c r="I2" t="n">
         <v>2.79</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>56.73</v>
+        <v>53.88</v>
       </c>
       <c r="D3" t="n">
         <v>37.18</v>
@@ -537,7 +537,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-34.5%</t>
+          <t>-31.0%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>394899</v>
+        <v>354758</v>
       </c>
       <c r="I3" t="n">
         <v>2.49</v>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>38.38</v>
+        <v>36.49</v>
       </c>
       <c r="D4" t="n">
         <v>26.54</v>
@@ -574,7 +574,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-30.9%</t>
+          <t>-27.3%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>406711</v>
+        <v>362565</v>
       </c>
       <c r="I4" t="n">
         <v>2.57</v>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>57.65401264230358</v>
+        <v>56.76420945127393</v>
       </c>
       <c r="D5" t="n">
         <v>38.63</v>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-33.0%</t>
+          <t>-32.0%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>346197</v>
+        <v>335176</v>
       </c>
       <c r="I5" t="n">
         <v>2.35</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>72.27</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="D6" t="n">
         <v>79.42</v>
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+9.9%</t>
+          <t>+13.3%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>22904</v>
+        <v>3984</v>
       </c>
       <c r="I6" t="n">
         <v>1.9</v>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6.29</v>
+        <v>6.05</v>
       </c>
       <c r="D7" t="n">
         <v>3.09</v>
@@ -685,7 +685,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-50.8%</t>
+          <t>-48.9%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>445150</v>
+        <v>418109</v>
       </c>
       <c r="I7" t="n">
         <v>2.21</v>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>30.81</v>
+        <v>30.67</v>
       </c>
       <c r="D8" t="n">
         <v>28.16</v>
@@ -722,7 +722,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>206030</v>
+        <v>198475</v>
       </c>
       <c r="I8" t="n">
         <v>0.71</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.685</v>
+        <v>22.19</v>
       </c>
       <c r="D9" t="n">
         <v>32.08</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+41.4%</t>
+          <t>+44.6%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>77.87</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="D10" t="n">
         <v>76.13</v>
@@ -796,7 +796,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>65353</v>
+        <v>58027</v>
       </c>
       <c r="I10" t="n">
         <v>1.77</v>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7.48</v>
+        <v>7.25</v>
       </c>
       <c r="D11" t="n">
         <v>5.99</v>
@@ -833,7 +833,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-20.0%</t>
+          <t>-17.4%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>93560</v>
+        <v>86423</v>
       </c>
       <c r="I11" t="n">
         <v>1.66</v>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29.425</v>
+        <v>28.45</v>
       </c>
       <c r="D12" t="n">
         <v>30.97</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+5.3%</t>
+          <t>+8.9%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>37275</v>
+        <v>30223</v>
       </c>
       <c r="I12" t="n">
         <v>1.67</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.18</v>
+        <v>15.4</v>
       </c>
       <c r="D13" t="n">
         <v>16.75</v>
@@ -907,7 +907,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+3.5%</t>
+          <t>+8.8%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>19623</v>
+        <v>12560</v>
       </c>
       <c r="I13" t="n">
         <v>1.38</v>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>39.75</v>
+        <v>37.62</v>
       </c>
       <c r="D14" t="n">
         <v>59.66</v>
@@ -944,7 +944,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+50.1%</t>
+          <t>+58.6%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>19.94</v>
+        <v>18.81</v>
       </c>
       <c r="D15" t="n">
         <v>20.52</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+2.9%</t>
+          <t>+9.1%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>18395</v>
+        <v>11242</v>
       </c>
       <c r="I15" t="n">
         <v>1.44</v>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>26.56</v>
+        <v>24.9</v>
       </c>
       <c r="D16" t="n">
         <v>28.5</v>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+7.3%</t>
+          <t>+14.4%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>15250</v>
+        <v>8685</v>
       </c>
       <c r="I16" t="n">
         <v>1.49</v>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>25.45</v>
+        <v>24.12</v>
       </c>
       <c r="D17" t="n">
         <v>23.98</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>36008</v>
+        <v>27466</v>
       </c>
       <c r="I17" t="n">
         <v>1.43</v>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>13.3972</v>
+        <v>12.718</v>
       </c>
       <c r="D18" t="n">
         <v>16.03</v>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+19.6%</t>
+          <t>+26.0%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.5376</v>
+        <v>2.4844</v>
       </c>
       <c r="D19" t="n">
         <v>2.21</v>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-11.1%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>137011</v>
+        <v>123507</v>
       </c>
       <c r="I19" t="n">
         <v>1.31</v>
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>41.24</v>
+        <v>40.16</v>
       </c>
       <c r="D20" t="n">
         <v>43.06</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+4.4%</t>
+          <t>+7.2%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>46961</v>
+        <v>21682</v>
       </c>
       <c r="I20" t="n">
         <v>1.49</v>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5.5727</v>
+        <v>5.5025</v>
       </c>
       <c r="D21" t="n">
         <v>9.27</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+66.4%</t>
+          <t>+68.5%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>15.78</v>
+        <v>14.96</v>
       </c>
       <c r="D22" t="n">
         <v>15.25</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>+1.9%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>58887</v>
+        <v>44838</v>
       </c>
       <c r="I22" t="n">
         <v>1.73</v>
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7.13</v>
+        <v>6.82</v>
       </c>
       <c r="D23" t="n">
         <v>9.779999999999999</v>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+37.2%</t>
+          <t>+43.4%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>41.63</v>
+        <v>41.03</v>
       </c>
       <c r="D24" t="n">
         <v>32.76</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-21.3%</t>
+          <t>-20.1%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>157417</v>
+        <v>150318</v>
       </c>
       <c r="I24" t="n">
         <v>1.59</v>
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>21.1556</v>
+        <v>20.3488</v>
       </c>
       <c r="D25" t="n">
         <v>15.43</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-27.0%</t>
+          <t>-24.2%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>186184</v>
+        <v>167334</v>
       </c>
       <c r="I25" t="n">
         <v>1.59</v>
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.3905</v>
+        <v>0.3955</v>
       </c>
       <c r="D26" t="n">
         <v>0.38</v>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>18872</v>
+        <v>19858</v>
       </c>
       <c r="I26" t="n">
         <v>1.22</v>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -493,23 +493,23 @@
         <v>17.41</v>
       </c>
       <c r="D2" t="n">
-        <v>14.95</v>
+        <v>14.68</v>
       </c>
       <c r="E2" t="n">
         <v>16</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-14.1%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>335008</v>
+        <v>354792</v>
       </c>
       <c r="I2" t="n">
         <v>2.79</v>
@@ -530,7 +530,7 @@
         <v>53.88</v>
       </c>
       <c r="D3" t="n">
-        <v>37.18</v>
+        <v>37.19</v>
       </c>
       <c r="E3" t="n">
         <v>45</v>
@@ -542,11 +542,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-17.4%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>354758</v>
+        <v>353871</v>
       </c>
       <c r="I3" t="n">
         <v>2.49</v>
@@ -567,23 +567,23 @@
         <v>36.49</v>
       </c>
       <c r="D4" t="n">
-        <v>26.54</v>
+        <v>26.41</v>
       </c>
       <c r="E4" t="n">
         <v>30.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-27.3%</t>
+          <t>-27.6%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-13.4%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>362565</v>
+        <v>365027</v>
       </c>
       <c r="I4" t="n">
         <v>2.57</v>
@@ -601,29 +601,29 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>56.76420945127393</v>
+        <v>56.66969897621367</v>
       </c>
       <c r="D5" t="n">
-        <v>38.63</v>
+        <v>38.5</v>
       </c>
       <c r="E5" t="n">
-        <v>52.01423065210093</v>
+        <v>51.92762872993299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-32.0%</t>
+          <t>-32.1%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-25.7%</t>
+          <t>-25.9%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>335176</v>
+        <v>333611</v>
       </c>
       <c r="I5" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="6">
@@ -641,23 +641,23 @@
         <v>70.06999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>79.42</v>
+        <v>79.61</v>
       </c>
       <c r="E6" t="n">
         <v>75</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+13.3%</t>
+          <t>+13.6%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+5.9%</t>
+          <t>+6.1%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3984</v>
+        <v>2343</v>
       </c>
       <c r="I6" t="n">
         <v>1.9</v>
@@ -678,23 +678,23 @@
         <v>6.05</v>
       </c>
       <c r="D7" t="n">
-        <v>3.09</v>
+        <v>3.14</v>
       </c>
       <c r="E7" t="n">
         <v>6</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-48.9%</t>
+          <t>-48.1%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-48.4%</t>
+          <t>-47.7%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>418109</v>
+        <v>413067</v>
       </c>
       <c r="I7" t="n">
         <v>2.21</v>
@@ -789,23 +789,23 @@
         <v>76.48999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>76.13</v>
+        <v>75.86</v>
       </c>
       <c r="E10" t="n">
         <v>94</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-19.0%</t>
+          <t>-19.3%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>58027</v>
+        <v>59337</v>
       </c>
       <c r="I10" t="n">
         <v>1.77</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>86423</v>
+        <v>86362</v>
       </c>
       <c r="I11" t="n">
         <v>1.66</v>
@@ -863,23 +863,23 @@
         <v>28.45</v>
       </c>
       <c r="D12" t="n">
-        <v>30.97</v>
+        <v>30.94</v>
       </c>
       <c r="E12" t="n">
         <v>25</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+8.9%</t>
+          <t>+8.7%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+23.9%</t>
+          <t>+23.8%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>30223</v>
+        <v>30419</v>
       </c>
       <c r="I12" t="n">
         <v>1.67</v>
@@ -900,23 +900,23 @@
         <v>15.4</v>
       </c>
       <c r="D13" t="n">
-        <v>16.75</v>
+        <v>16.77</v>
       </c>
       <c r="E13" t="n">
         <v>17.95</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+8.8%</t>
+          <t>+8.9%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>12560</v>
+        <v>12385</v>
       </c>
       <c r="I13" t="n">
         <v>1.38</v>
@@ -937,19 +937,19 @@
         <v>37.62</v>
       </c>
       <c r="D14" t="n">
-        <v>59.66</v>
+        <v>59.78</v>
       </c>
       <c r="E14" t="n">
         <v>51.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+58.6%</t>
+          <t>+58.9%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+15.8%</t>
+          <t>+16.1%</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -974,23 +974,23 @@
         <v>18.81</v>
       </c>
       <c r="D15" t="n">
-        <v>20.52</v>
+        <v>20.98</v>
       </c>
       <c r="E15" t="n">
         <v>27.98</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+9.1%</t>
+          <t>+11.5%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-26.6%</t>
+          <t>-25.0%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>11242</v>
+        <v>8328</v>
       </c>
       <c r="I15" t="n">
         <v>1.44</v>
@@ -1011,26 +1011,26 @@
         <v>24.9</v>
       </c>
       <c r="D16" t="n">
-        <v>28.5</v>
+        <v>29.16</v>
       </c>
       <c r="E16" t="n">
         <v>34.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+14.4%</t>
+          <t>+17.1%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-17.4%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>8685</v>
+        <v>5782</v>
       </c>
       <c r="I16" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="17">
@@ -1048,23 +1048,23 @@
         <v>24.12</v>
       </c>
       <c r="D17" t="n">
-        <v>23.98</v>
+        <v>24.65</v>
       </c>
       <c r="E17" t="n">
         <v>24.8</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>+2.2%</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t>-0.6%</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>-3.3%</t>
-        </is>
-      </c>
       <c r="H17" t="n">
-        <v>27466</v>
+        <v>23026</v>
       </c>
       <c r="I17" t="n">
         <v>1.43</v>
@@ -1233,23 +1233,23 @@
         <v>14.96</v>
       </c>
       <c r="D22" t="n">
-        <v>15.25</v>
+        <v>15.48</v>
       </c>
       <c r="E22" t="n">
         <v>16.59</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+1.9%</t>
+          <t>+3.5%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>44838</v>
+        <v>40715</v>
       </c>
       <c r="I22" t="n">
         <v>1.73</v>
@@ -1270,19 +1270,19 @@
         <v>6.82</v>
       </c>
       <c r="D23" t="n">
-        <v>9.779999999999999</v>
+        <v>9.82</v>
       </c>
       <c r="E23" t="n">
         <v>7.1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+43.4%</t>
+          <t>+44.0%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+37.8%</t>
+          <t>+38.4%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1388,16 +1388,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-13.8%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>19858</v>
+        <v>18543</v>
       </c>
       <c r="I26" t="n">
         <v>1.22</v>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -1270,19 +1270,19 @@
         <v>6.82</v>
       </c>
       <c r="D23" t="n">
-        <v>9.82</v>
+        <v>9.69</v>
       </c>
       <c r="E23" t="n">
         <v>7.1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+44.0%</t>
+          <t>+42.1%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+38.4%</t>
+          <t>+36.5%</t>
         </is>
       </c>
       <c r="H23" t="n">

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.41</v>
+        <v>17.89</v>
       </c>
       <c r="D2" t="n">
         <v>14.68</v>
@@ -500,7 +500,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-17.9%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>354792</v>
+        <v>389978</v>
       </c>
       <c r="I2" t="n">
         <v>2.79</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>53.88</v>
+        <v>54.24</v>
       </c>
       <c r="D3" t="n">
         <v>37.19</v>
@@ -537,7 +537,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-31.0%</t>
+          <t>-31.4%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>353871</v>
+        <v>358931</v>
       </c>
       <c r="I3" t="n">
         <v>2.49</v>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>36.49</v>
+        <v>36.93</v>
       </c>
       <c r="D4" t="n">
         <v>26.41</v>
@@ -574,7 +574,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-27.6%</t>
+          <t>-28.5%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>365027</v>
+        <v>375292</v>
       </c>
       <c r="I4" t="n">
         <v>2.57</v>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>56.66969897621367</v>
+        <v>57.74091043680599</v>
       </c>
       <c r="D5" t="n">
         <v>38.5</v>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-32.1%</t>
+          <t>-33.3%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>333611</v>
+        <v>346802</v>
       </c>
       <c r="I5" t="n">
         <v>2.34</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>70.06999999999999</v>
+        <v>71.91</v>
       </c>
       <c r="D6" t="n">
         <v>79.61</v>
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+13.6%</t>
+          <t>+10.7%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2343</v>
+        <v>18151</v>
       </c>
       <c r="I6" t="n">
         <v>1.9</v>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6.05</v>
+        <v>6.16</v>
       </c>
       <c r="D7" t="n">
         <v>3.14</v>
@@ -685,7 +685,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-48.1%</t>
+          <t>-49.1%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>413067</v>
+        <v>425461</v>
       </c>
       <c r="I7" t="n">
         <v>2.21</v>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>30.67</v>
+        <v>30.56</v>
       </c>
       <c r="D8" t="n">
         <v>28.16</v>
@@ -722,7 +722,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>198475</v>
+        <v>192539</v>
       </c>
       <c r="I8" t="n">
         <v>0.71</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.19</v>
+        <v>22.46</v>
       </c>
       <c r="D9" t="n">
         <v>32.08</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+44.6%</t>
+          <t>+42.9%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>76.48999999999999</v>
+        <v>77.98</v>
       </c>
       <c r="D10" t="n">
         <v>75.86</v>
@@ -796,7 +796,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>59337</v>
+        <v>67231</v>
       </c>
       <c r="I10" t="n">
         <v>1.77</v>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7.25</v>
+        <v>7.33</v>
       </c>
       <c r="D11" t="n">
         <v>5.99</v>
@@ -833,7 +833,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-17.4%</t>
+          <t>-18.3%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>86362</v>
+        <v>88842</v>
       </c>
       <c r="I11" t="n">
         <v>1.66</v>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>28.45</v>
+        <v>29.08</v>
       </c>
       <c r="D12" t="n">
         <v>30.94</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+8.7%</t>
+          <t>+6.4%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>30419</v>
+        <v>34968</v>
       </c>
       <c r="I12" t="n">
         <v>1.67</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>15.4</v>
+        <v>15.82</v>
       </c>
       <c r="D13" t="n">
         <v>16.77</v>
@@ -907,7 +907,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+8.9%</t>
+          <t>+6.0%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>12385</v>
+        <v>16227</v>
       </c>
       <c r="I13" t="n">
         <v>1.38</v>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>37.62</v>
+        <v>38.86</v>
       </c>
       <c r="D14" t="n">
         <v>59.78</v>
@@ -944,7 +944,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+58.9%</t>
+          <t>+53.8%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>18.81</v>
+        <v>18.63</v>
       </c>
       <c r="D15" t="n">
         <v>20.98</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+11.5%</t>
+          <t>+12.6%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>8328</v>
+        <v>7192</v>
       </c>
       <c r="I15" t="n">
         <v>1.44</v>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24.9</v>
+        <v>26.09</v>
       </c>
       <c r="D16" t="n">
         <v>29.16</v>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+17.1%</t>
+          <t>+11.8%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5782</v>
+        <v>10780</v>
       </c>
       <c r="I16" t="n">
         <v>1.48</v>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24.12</v>
+        <v>25.26</v>
       </c>
       <c r="D17" t="n">
         <v>24.65</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+2.2%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>23026</v>
+        <v>30323</v>
       </c>
       <c r="I17" t="n">
         <v>1.43</v>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>12.718</v>
+        <v>12.6039</v>
       </c>
       <c r="D18" t="n">
         <v>16.03</v>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+26.0%</t>
+          <t>+27.2%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.4844</v>
+        <v>2.4627</v>
       </c>
       <c r="D19" t="n">
         <v>2.21</v>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-11.1%</t>
+          <t>-10.2%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>123507</v>
+        <v>117818</v>
       </c>
       <c r="I19" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="20">
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>40.16</v>
+        <v>41.1</v>
       </c>
       <c r="D20" t="n">
         <v>43.06</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+7.2%</t>
+          <t>+4.8%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>21682</v>
+        <v>43684</v>
       </c>
       <c r="I20" t="n">
         <v>1.49</v>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5.5025</v>
+        <v>5.4152</v>
       </c>
       <c r="D21" t="n">
         <v>9.27</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+68.5%</t>
+          <t>+71.2%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>14.96</v>
+        <v>15.08</v>
       </c>
       <c r="D22" t="n">
         <v>15.48</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+3.5%</t>
+          <t>+2.7%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>40715</v>
+        <v>42767</v>
       </c>
       <c r="I22" t="n">
         <v>1.73</v>
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6.82</v>
+        <v>7.16</v>
       </c>
       <c r="D23" t="n">
         <v>9.69</v>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+42.1%</t>
+          <t>+35.4%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>41.03</v>
+        <v>43.09</v>
       </c>
       <c r="D24" t="n">
         <v>32.76</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-20.1%</t>
+          <t>-24.0%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>150318</v>
+        <v>174694</v>
       </c>
       <c r="I24" t="n">
         <v>1.59</v>
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>20.3488</v>
+        <v>21.1029</v>
       </c>
       <c r="D25" t="n">
         <v>15.43</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-24.2%</t>
+          <t>-26.9%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>167334</v>
+        <v>184952</v>
       </c>
       <c r="I25" t="n">
         <v>1.59</v>
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.3955</v>
+        <v>0.3941</v>
       </c>
       <c r="D26" t="n">
         <v>0.38</v>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>18543</v>
+        <v>18267</v>
       </c>
       <c r="I26" t="n">
         <v>1.22</v>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -974,26 +974,26 @@
         <v>18.63</v>
       </c>
       <c r="D15" t="n">
-        <v>20.98</v>
+        <v>21.01</v>
       </c>
       <c r="E15" t="n">
         <v>27.98</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+12.6%</t>
+          <t>+12.8%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-24.9%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>7192</v>
+        <v>7186</v>
       </c>
       <c r="I15" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="16">
@@ -1011,26 +1011,26 @@
         <v>26.09</v>
       </c>
       <c r="D16" t="n">
-        <v>29.16</v>
+        <v>29.22</v>
       </c>
       <c r="E16" t="n">
         <v>34.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+11.8%</t>
+          <t>+12.0%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>10780</v>
+        <v>10759</v>
       </c>
       <c r="I16" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="17">
@@ -1048,26 +1048,26 @@
         <v>25.26</v>
       </c>
       <c r="D17" t="n">
-        <v>24.65</v>
+        <v>24.71</v>
       </c>
       <c r="E17" t="n">
         <v>24.8</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>30323</v>
+        <v>30248</v>
       </c>
       <c r="I17" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="18">
@@ -1233,26 +1233,26 @@
         <v>15.08</v>
       </c>
       <c r="D22" t="n">
-        <v>15.48</v>
+        <v>15.5</v>
       </c>
       <c r="E22" t="n">
         <v>16.59</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+2.7%</t>
+          <t>+2.8%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>42767</v>
+        <v>42607</v>
       </c>
       <c r="I22" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="23">
@@ -1270,26 +1270,26 @@
         <v>7.16</v>
       </c>
       <c r="D23" t="n">
-        <v>9.69</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E23" t="n">
         <v>7.1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+35.4%</t>
+          <t>+35.5%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+36.5%</t>
+          <t>+36.6%</t>
         </is>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="24">
@@ -1388,19 +1388,19 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-13.8%</t>
+          <t>-13.6%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>18267</v>
+        <v>18360</v>
       </c>
       <c r="I26" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.89</v>
+        <v>18.45</v>
       </c>
       <c r="D2" t="n">
         <v>14.68</v>
@@ -500,7 +500,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-17.9%</t>
+          <t>-20.4%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>389978</v>
+        <v>431028</v>
       </c>
       <c r="I2" t="n">
         <v>2.79</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>54.24</v>
+        <v>57.88</v>
       </c>
       <c r="D3" t="n">
         <v>37.19</v>
@@ -537,7 +537,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-31.4%</t>
+          <t>-35.7%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>358931</v>
+        <v>410092</v>
       </c>
       <c r="I3" t="n">
         <v>2.49</v>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>36.93</v>
+        <v>39.29</v>
       </c>
       <c r="D4" t="n">
         <v>26.41</v>
@@ -574,7 +574,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-28.5%</t>
+          <t>-32.8%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>375292</v>
+        <v>430349</v>
       </c>
       <c r="I4" t="n">
         <v>2.57</v>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>57.74091043680599</v>
+        <v>60.27523998991467</v>
       </c>
       <c r="D5" t="n">
         <v>38.5</v>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-33.3%</t>
+          <t>-36.1%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>346802</v>
+        <v>378011</v>
       </c>
       <c r="I5" t="n">
         <v>2.34</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>71.91</v>
+        <v>75.81</v>
       </c>
       <c r="D6" t="n">
         <v>79.61</v>
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+10.7%</t>
+          <t>+5.0%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>18151</v>
+        <v>51652</v>
       </c>
       <c r="I6" t="n">
         <v>1.9</v>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6.16</v>
+        <v>6.45</v>
       </c>
       <c r="D7" t="n">
         <v>3.14</v>
@@ -685,7 +685,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-49.1%</t>
+          <t>-51.3%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>425461</v>
+        <v>458136</v>
       </c>
       <c r="I7" t="n">
         <v>2.21</v>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>30.56</v>
+        <v>30.85</v>
       </c>
       <c r="D8" t="n">
         <v>28.16</v>
@@ -722,7 +722,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>192539</v>
+        <v>208188</v>
       </c>
       <c r="I8" t="n">
         <v>0.71</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.46</v>
+        <v>23.35</v>
       </c>
       <c r="D9" t="n">
         <v>32.08</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+42.9%</t>
+          <t>+37.4%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>77.98</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="D10" t="n">
         <v>75.86</v>
@@ -796,7 +796,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>67231</v>
+        <v>75231</v>
       </c>
       <c r="I10" t="n">
         <v>1.77</v>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7.33</v>
+        <v>7.65</v>
       </c>
       <c r="D11" t="n">
         <v>5.99</v>
@@ -833,7 +833,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-18.3%</t>
+          <t>-21.8%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>88842</v>
+        <v>98762</v>
       </c>
       <c r="I11" t="n">
         <v>1.66</v>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29.08</v>
+        <v>30.28</v>
       </c>
       <c r="D12" t="n">
         <v>30.94</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+6.4%</t>
+          <t>+2.2%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>34968</v>
+        <v>43631</v>
       </c>
       <c r="I12" t="n">
         <v>1.67</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>15.82</v>
+        <v>16.61</v>
       </c>
       <c r="D13" t="n">
         <v>16.77</v>
@@ -907,7 +907,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+6.0%</t>
+          <t>+1.0%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>16227</v>
+        <v>23306</v>
       </c>
       <c r="I13" t="n">
         <v>1.38</v>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>38.86</v>
+        <v>39.4</v>
       </c>
       <c r="D14" t="n">
         <v>59.78</v>
@@ -944,7 +944,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+53.8%</t>
+          <t>+51.7%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>18.63</v>
+        <v>18.84</v>
       </c>
       <c r="D15" t="n">
         <v>21.01</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+12.8%</t>
+          <t>+11.5%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>7186</v>
+        <v>8510</v>
       </c>
       <c r="I15" t="n">
         <v>1.45</v>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>26.09</v>
+        <v>28.14</v>
       </c>
       <c r="D16" t="n">
         <v>29.22</v>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+12.0%</t>
+          <t>+3.8%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>10759</v>
+        <v>18761</v>
       </c>
       <c r="I16" t="n">
         <v>1.49</v>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>25.26</v>
+        <v>26.77</v>
       </c>
       <c r="D17" t="n">
         <v>24.71</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>30248</v>
+        <v>39889</v>
       </c>
       <c r="I17" t="n">
         <v>1.44</v>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>12.6039</v>
+        <v>13.0112</v>
       </c>
       <c r="D18" t="n">
         <v>16.03</v>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+27.2%</t>
+          <t>+23.2%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.4627</v>
+        <v>2.5974</v>
       </c>
       <c r="D19" t="n">
         <v>2.21</v>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-10.2%</t>
+          <t>-14.9%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>117818</v>
+        <v>151957</v>
       </c>
       <c r="I19" t="n">
         <v>1.32</v>
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>41.1</v>
+        <v>43.61</v>
       </c>
       <c r="D20" t="n">
         <v>43.06</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+4.8%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>43684</v>
+        <v>102435</v>
       </c>
       <c r="I20" t="n">
         <v>1.49</v>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5.4152</v>
+        <v>5.7234</v>
       </c>
       <c r="D21" t="n">
         <v>9.27</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+71.2%</t>
+          <t>+62.0%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>15.08</v>
+        <v>15.74</v>
       </c>
       <c r="D22" t="n">
         <v>15.5</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+2.8%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>42607</v>
+        <v>53850</v>
       </c>
       <c r="I22" t="n">
         <v>1.72</v>
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7.16</v>
+        <v>7.67</v>
       </c>
       <c r="D23" t="n">
         <v>9.699999999999999</v>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+35.5%</t>
+          <t>+26.5%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>43.09</v>
+        <v>45.32</v>
       </c>
       <c r="D24" t="n">
         <v>32.76</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-24.0%</t>
+          <t>-27.7%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>174694</v>
+        <v>201081</v>
       </c>
       <c r="I24" t="n">
         <v>1.59</v>
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>21.1029</v>
+        <v>21.9952</v>
       </c>
       <c r="D25" t="n">
         <v>15.43</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-26.9%</t>
+          <t>-29.8%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>184952</v>
+        <v>205800</v>
       </c>
       <c r="I25" t="n">
         <v>1.59</v>
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.3941</v>
+        <v>0.4208</v>
       </c>
       <c r="D26" t="n">
         <v>0.38</v>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>18360</v>
+        <v>23656</v>
       </c>
       <c r="I26" t="n">
         <v>1.24</v>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -974,23 +974,23 @@
         <v>18.84</v>
       </c>
       <c r="D15" t="n">
-        <v>21.01</v>
+        <v>21.34</v>
       </c>
       <c r="E15" t="n">
         <v>27.98</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+11.5%</t>
+          <t>+13.3%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-24.9%</t>
+          <t>-23.7%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>8510</v>
+        <v>6450</v>
       </c>
       <c r="I15" t="n">
         <v>1.45</v>
@@ -1011,26 +1011,26 @@
         <v>28.14</v>
       </c>
       <c r="D16" t="n">
-        <v>29.22</v>
+        <v>29.66</v>
       </c>
       <c r="E16" t="n">
         <v>34.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+3.8%</t>
+          <t>+5.4%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-14.0%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>18761</v>
+        <v>16990</v>
       </c>
       <c r="I16" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="17">
@@ -1048,23 +1048,23 @@
         <v>26.77</v>
       </c>
       <c r="D17" t="n">
-        <v>24.71</v>
+        <v>25.14</v>
       </c>
       <c r="E17" t="n">
         <v>24.8</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>+1.4%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>39889</v>
+        <v>37010</v>
       </c>
       <c r="I17" t="n">
         <v>1.44</v>
@@ -1233,23 +1233,23 @@
         <v>15.74</v>
       </c>
       <c r="D22" t="n">
-        <v>15.5</v>
+        <v>15.57</v>
       </c>
       <c r="E22" t="n">
         <v>16.59</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>53850</v>
+        <v>52675</v>
       </c>
       <c r="I22" t="n">
         <v>1.72</v>
@@ -1270,19 +1270,19 @@
         <v>7.67</v>
       </c>
       <c r="D23" t="n">
-        <v>9.699999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="E23" t="n">
         <v>7.1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+26.5%</t>
+          <t>+27.1%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+36.6%</t>
+          <t>+37.3%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1381,23 +1381,23 @@
         <v>0.4208</v>
       </c>
       <c r="D26" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="E26" t="n">
         <v>0.443</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-13.6%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>23656</v>
+        <v>22622</v>
       </c>
       <c r="I26" t="n">
         <v>1.24</v>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18.45</v>
+        <v>18.665</v>
       </c>
       <c r="D2" t="n">
         <v>14.68</v>
@@ -500,7 +500,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-20.4%</t>
+          <t>-21.3%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>431028</v>
+        <v>446788</v>
       </c>
       <c r="I2" t="n">
         <v>2.79</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>57.88</v>
+        <v>60.48</v>
       </c>
       <c r="D3" t="n">
         <v>37.19</v>
@@ -537,7 +537,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-35.7%</t>
+          <t>-38.5%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>410092</v>
+        <v>446636</v>
       </c>
       <c r="I3" t="n">
         <v>2.49</v>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>39.29</v>
+        <v>39.34</v>
       </c>
       <c r="D4" t="n">
         <v>26.41</v>
@@ -574,7 +574,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-32.8%</t>
+          <t>-32.9%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>430349</v>
+        <v>431515</v>
       </c>
       <c r="I4" t="n">
         <v>2.57</v>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>60.27523998991467</v>
+        <v>62.78997421142714</v>
       </c>
       <c r="D5" t="n">
         <v>38.5</v>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-36.1%</t>
+          <t>-38.7%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>378011</v>
+        <v>408978</v>
       </c>
       <c r="I5" t="n">
         <v>2.34</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>75.81</v>
+        <v>79.955</v>
       </c>
       <c r="D6" t="n">
         <v>79.61</v>
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+5.0%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>51652</v>
+        <v>87258</v>
       </c>
       <c r="I6" t="n">
         <v>1.9</v>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6.45</v>
+        <v>6.525</v>
       </c>
       <c r="D7" t="n">
         <v>3.14</v>
@@ -685,7 +685,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-51.3%</t>
+          <t>-51.9%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>458136</v>
+        <v>466586</v>
       </c>
       <c r="I7" t="n">
         <v>2.21</v>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>30.85</v>
+        <v>31.155</v>
       </c>
       <c r="D8" t="n">
         <v>28.16</v>
@@ -722,7 +722,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>208188</v>
+        <v>224647</v>
       </c>
       <c r="I8" t="n">
         <v>0.71</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23.35</v>
+        <v>22.39</v>
       </c>
       <c r="D9" t="n">
         <v>32.08</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+37.4%</t>
+          <t>+43.3%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>79.48999999999999</v>
+        <v>77.36499999999999</v>
       </c>
       <c r="D10" t="n">
         <v>75.86</v>
@@ -796,7 +796,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>75231</v>
+        <v>63973</v>
       </c>
       <c r="I10" t="n">
         <v>1.77</v>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7.65</v>
+        <v>7.67</v>
       </c>
       <c r="D11" t="n">
         <v>5.99</v>
@@ -833,7 +833,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-21.8%</t>
+          <t>-22.0%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>98762</v>
+        <v>99382</v>
       </c>
       <c r="I11" t="n">
         <v>1.66</v>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>30.28</v>
+        <v>30.19</v>
       </c>
       <c r="D12" t="n">
         <v>30.94</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+2.2%</t>
+          <t>+2.5%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>43631</v>
+        <v>42981</v>
       </c>
       <c r="I12" t="n">
         <v>1.67</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.61</v>
+        <v>17.4</v>
       </c>
       <c r="D13" t="n">
         <v>16.77</v>
@@ -907,7 +907,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+1.0%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>23306</v>
+        <v>30382</v>
       </c>
       <c r="I13" t="n">
         <v>1.38</v>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>39.4</v>
+        <v>40.23</v>
       </c>
       <c r="D14" t="n">
         <v>59.78</v>
@@ -944,7 +944,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+51.7%</t>
+          <t>+48.6%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>18.84</v>
+        <v>19.305</v>
       </c>
       <c r="D15" t="n">
         <v>21.34</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+13.3%</t>
+          <t>+10.5%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>6450</v>
+        <v>9375</v>
       </c>
       <c r="I15" t="n">
         <v>1.45</v>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>28.14</v>
+        <v>28.77</v>
       </c>
       <c r="D16" t="n">
         <v>29.66</v>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+5.4%</t>
+          <t>+3.1%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>16990</v>
+        <v>19445</v>
       </c>
       <c r="I16" t="n">
         <v>1.48</v>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26.77</v>
+        <v>25.76</v>
       </c>
       <c r="D17" t="n">
         <v>25.14</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>37010</v>
+        <v>30584</v>
       </c>
       <c r="I17" t="n">
         <v>1.44</v>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>13.0112</v>
+        <v>13.5056</v>
       </c>
       <c r="D18" t="n">
         <v>16.03</v>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+23.2%</t>
+          <t>+18.7%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.5974</v>
+        <v>2.5699</v>
       </c>
       <c r="D19" t="n">
         <v>2.21</v>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-14.0%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>151957</v>
+        <v>144987</v>
       </c>
       <c r="I19" t="n">
         <v>1.32</v>
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>43.61</v>
+        <v>44.303</v>
       </c>
       <c r="D20" t="n">
         <v>43.06</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>102435</v>
+        <v>118655</v>
       </c>
       <c r="I20" t="n">
         <v>1.49</v>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5.7234</v>
+        <v>5.9711</v>
       </c>
       <c r="D21" t="n">
         <v>9.27</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+62.0%</t>
+          <t>+55.3%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>15.74</v>
+        <v>16.16</v>
       </c>
       <c r="D22" t="n">
         <v>15.57</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>52675</v>
+        <v>59822</v>
       </c>
       <c r="I22" t="n">
         <v>1.72</v>
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7.67</v>
+        <v>7.81</v>
       </c>
       <c r="D23" t="n">
         <v>9.75</v>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+27.1%</t>
+          <t>+24.8%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>45.32</v>
+        <v>46.54</v>
       </c>
       <c r="D24" t="n">
         <v>32.76</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-27.7%</t>
+          <t>-29.6%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>201081</v>
+        <v>215517</v>
       </c>
       <c r="I24" t="n">
         <v>1.59</v>
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>21.9952</v>
+        <v>22.7028</v>
       </c>
       <c r="D25" t="n">
         <v>15.43</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-29.8%</t>
+          <t>-32.0%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>205800</v>
+        <v>222333</v>
       </c>
       <c r="I25" t="n">
         <v>1.59</v>
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.4208</v>
+        <v>0.4183</v>
       </c>
       <c r="D26" t="n">
         <v>0.39</v>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>22622</v>
+        <v>22126</v>
       </c>
       <c r="I26" t="n">
         <v>1.24</v>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -1270,19 +1270,19 @@
         <v>7.81</v>
       </c>
       <c r="D23" t="n">
-        <v>9.75</v>
+        <v>10.35</v>
       </c>
       <c r="E23" t="n">
         <v>7.1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+24.8%</t>
+          <t>+32.5%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+37.3%</t>
+          <t>+45.7%</t>
         </is>
       </c>
       <c r="H23" t="n">

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -641,26 +641,26 @@
         <v>79.955</v>
       </c>
       <c r="D6" t="n">
-        <v>79.61</v>
+        <v>83.25</v>
       </c>
       <c r="E6" t="n">
         <v>75</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>+4.1%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+6.1%</t>
+          <t>+11.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>87258</v>
+        <v>54688</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="7">

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -641,26 +641,26 @@
         <v>79.955</v>
       </c>
       <c r="D6" t="n">
-        <v>83.25</v>
+        <v>79.61</v>
       </c>
       <c r="E6" t="n">
         <v>75</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+4.1%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+11.0%</t>
+          <t>+6.1%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>54688</v>
+        <v>87258</v>
       </c>
       <c r="I6" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="7">
@@ -1270,19 +1270,19 @@
         <v>7.81</v>
       </c>
       <c r="D23" t="n">
-        <v>10.35</v>
+        <v>9.75</v>
       </c>
       <c r="E23" t="n">
         <v>7.1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+32.5%</t>
+          <t>+24.8%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+45.7%</t>
+          <t>+37.3%</t>
         </is>
       </c>
       <c r="H23" t="n">

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18.665</v>
+        <v>18.76</v>
       </c>
       <c r="D2" t="n">
         <v>14.68</v>
@@ -500,7 +500,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-21.3%</t>
+          <t>-21.7%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>446788</v>
+        <v>453752</v>
       </c>
       <c r="I2" t="n">
         <v>2.79</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>60.48</v>
+        <v>61.86</v>
       </c>
       <c r="D3" t="n">
         <v>37.19</v>
@@ -537,7 +537,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-38.5%</t>
+          <t>-39.9%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>446636</v>
+        <v>466032</v>
       </c>
       <c r="I3" t="n">
         <v>2.49</v>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>39.34</v>
+        <v>39.74</v>
       </c>
       <c r="D4" t="n">
         <v>26.41</v>
@@ -574,7 +574,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-32.9%</t>
+          <t>-33.5%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>431515</v>
+        <v>440847</v>
       </c>
       <c r="I4" t="n">
         <v>2.57</v>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>62.78997421142714</v>
+        <v>60.36015309349821</v>
       </c>
       <c r="D5" t="n">
         <v>38.5</v>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-38.7%</t>
+          <t>-36.2%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>408978</v>
+        <v>379056</v>
       </c>
       <c r="I5" t="n">
         <v>2.34</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>79.955</v>
+        <v>77.25</v>
       </c>
       <c r="D6" t="n">
         <v>79.61</v>
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>+3.1%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>87258</v>
+        <v>64022</v>
       </c>
       <c r="I6" t="n">
         <v>1.9</v>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6.525</v>
+        <v>6.46</v>
       </c>
       <c r="D7" t="n">
         <v>3.14</v>
@@ -685,7 +685,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-51.9%</t>
+          <t>-51.4%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>466586</v>
+        <v>459263</v>
       </c>
       <c r="I7" t="n">
         <v>2.21</v>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>31.155</v>
+        <v>30.84</v>
       </c>
       <c r="D8" t="n">
         <v>28.16</v>
@@ -722,7 +722,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>224647</v>
+        <v>207648</v>
       </c>
       <c r="I8" t="n">
         <v>0.71</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.39</v>
+        <v>22.37</v>
       </c>
       <c r="D9" t="n">
         <v>32.08</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+43.3%</t>
+          <t>+43.4%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>77.36499999999999</v>
+        <v>76.08</v>
       </c>
       <c r="D10" t="n">
         <v>75.86</v>
@@ -796,7 +796,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>63973</v>
+        <v>57165</v>
       </c>
       <c r="I10" t="n">
         <v>1.77</v>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7.67</v>
+        <v>7.51</v>
       </c>
       <c r="D11" t="n">
         <v>5.99</v>
@@ -833,7 +833,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-22.0%</t>
+          <t>-20.3%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>99382</v>
+        <v>94422</v>
       </c>
       <c r="I11" t="n">
         <v>1.66</v>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>30.19</v>
+        <v>29.49</v>
       </c>
       <c r="D12" t="n">
         <v>30.94</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+2.5%</t>
+          <t>+4.9%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>42981</v>
+        <v>37928</v>
       </c>
       <c r="I12" t="n">
         <v>1.67</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.4</v>
+        <v>16.71</v>
       </c>
       <c r="D13" t="n">
         <v>16.77</v>
@@ -907,7 +907,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>+0.4%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>30382</v>
+        <v>24202</v>
       </c>
       <c r="I13" t="n">
         <v>1.38</v>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>40.23</v>
+        <v>39.14</v>
       </c>
       <c r="D14" t="n">
         <v>59.78</v>
@@ -944,7 +944,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+48.6%</t>
+          <t>+52.7%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>19.305</v>
+        <v>17.8</v>
       </c>
       <c r="D15" t="n">
         <v>21.34</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+10.5%</t>
+          <t>+19.9%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>9375</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>1.45</v>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>28.77</v>
+        <v>28.9</v>
       </c>
       <c r="D16" t="n">
         <v>29.66</v>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+3.1%</t>
+          <t>+2.6%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>19445</v>
+        <v>19951</v>
       </c>
       <c r="I16" t="n">
         <v>1.48</v>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>25.76</v>
+        <v>25.33</v>
       </c>
       <c r="D17" t="n">
         <v>25.14</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>30584</v>
+        <v>27848</v>
       </c>
       <c r="I17" t="n">
         <v>1.44</v>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>13.5056</v>
+        <v>13.9395</v>
       </c>
       <c r="D18" t="n">
         <v>16.03</v>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+18.7%</t>
+          <t>+15.0%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>19107</v>
       </c>
       <c r="I18" t="n">
         <v>2.46</v>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.5699</v>
+        <v>2.5565</v>
       </c>
       <c r="D19" t="n">
         <v>2.21</v>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-14.0%</t>
+          <t>-13.5%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>144987</v>
+        <v>141591</v>
       </c>
       <c r="I19" t="n">
         <v>1.32</v>
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>44.303</v>
+        <v>42.44</v>
       </c>
       <c r="D20" t="n">
         <v>43.06</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>+1.5%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>118655</v>
+        <v>75049</v>
       </c>
       <c r="I20" t="n">
         <v>1.49</v>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5.9711</v>
+        <v>6.407</v>
       </c>
       <c r="D21" t="n">
         <v>9.27</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+55.3%</t>
+          <t>+44.7%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>16.16</v>
+        <v>16.29</v>
       </c>
       <c r="D22" t="n">
         <v>15.57</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>59822</v>
+        <v>62034</v>
       </c>
       <c r="I22" t="n">
         <v>1.72</v>
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7.81</v>
+        <v>7.6</v>
       </c>
       <c r="D23" t="n">
         <v>9.75</v>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+24.8%</t>
+          <t>+28.3%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>46.54</v>
+        <v>45.76</v>
       </c>
       <c r="D24" t="n">
         <v>32.76</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-29.6%</t>
+          <t>-28.4%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>215517</v>
+        <v>206288</v>
       </c>
       <c r="I24" t="n">
         <v>1.59</v>
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>22.7028</v>
+        <v>21.6026</v>
       </c>
       <c r="D25" t="n">
         <v>15.43</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-32.0%</t>
+          <t>-28.6%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>222333</v>
+        <v>196627</v>
       </c>
       <c r="I25" t="n">
         <v>1.59</v>
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.4183</v>
+        <v>0.4845</v>
       </c>
       <c r="D26" t="n">
         <v>0.39</v>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>22126</v>
+        <v>35266</v>
       </c>
       <c r="I26" t="n">
         <v>1.24</v>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -641,26 +641,26 @@
         <v>77.25</v>
       </c>
       <c r="D6" t="n">
-        <v>79.61</v>
+        <v>86.17</v>
       </c>
       <c r="E6" t="n">
         <v>75</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+3.1%</t>
+          <t>+11.6%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+6.1%</t>
+          <t>+14.9%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>64022</v>
+        <v>8968</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="7">
@@ -900,23 +900,23 @@
         <v>16.71</v>
       </c>
       <c r="D13" t="n">
-        <v>16.77</v>
+        <v>17.13</v>
       </c>
       <c r="E13" t="n">
         <v>17.95</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+0.4%</t>
+          <t>+2.5%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>24202</v>
+        <v>21597</v>
       </c>
       <c r="I13" t="n">
         <v>1.38</v>
@@ -1270,19 +1270,19 @@
         <v>7.6</v>
       </c>
       <c r="D23" t="n">
-        <v>9.75</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E23" t="n">
         <v>7.1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+28.3%</t>
+          <t>+27.6%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+37.3%</t>
+          <t>+36.6%</t>
         </is>
       </c>
       <c r="H23" t="n">

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -530,23 +530,23 @@
         <v>61.86</v>
       </c>
       <c r="D3" t="n">
-        <v>37.19</v>
+        <v>40.24</v>
       </c>
       <c r="E3" t="n">
         <v>45</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-39.9%</t>
+          <t>-34.9%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-10.6%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>466032</v>
+        <v>421886</v>
       </c>
       <c r="I3" t="n">
         <v>2.49</v>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -752,26 +752,26 @@
         <v>22.37</v>
       </c>
       <c r="D9" t="n">
-        <v>32.08</v>
+        <v>29.97</v>
       </c>
       <c r="E9" t="n">
         <v>25.17</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+43.4%</t>
+          <t>+34.0%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+27.5%</t>
+          <t>+19.1%</t>
         </is>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="10">

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -789,26 +789,26 @@
         <v>76.08</v>
       </c>
       <c r="D10" t="n">
-        <v>75.86</v>
+        <v>73.34</v>
       </c>
       <c r="E10" t="n">
         <v>94</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-19.3%</t>
+          <t>-22.0%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>57165</v>
+        <v>71456</v>
       </c>
       <c r="I10" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="11">

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -1307,23 +1307,23 @@
         <v>45.76</v>
       </c>
       <c r="D24" t="n">
-        <v>32.76</v>
+        <v>33.93</v>
       </c>
       <c r="E24" t="n">
         <v>54</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-28.4%</t>
+          <t>-25.9%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-39.3%</t>
+          <t>-37.2%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>206288</v>
+        <v>223619</v>
       </c>
       <c r="I24" t="n">
         <v>1.59</v>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -1159,23 +1159,23 @@
         <v>42.44</v>
       </c>
       <c r="D20" t="n">
-        <v>43.06</v>
+        <v>45.5</v>
       </c>
       <c r="E20" t="n">
         <v>52.04</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+1.5%</t>
+          <t>+7.2%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>75049</v>
+        <v>16874</v>
       </c>
       <c r="I20" t="n">
         <v>1.49</v>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -493,23 +493,23 @@
         <v>18.76</v>
       </c>
       <c r="D2" t="n">
-        <v>14.68</v>
+        <v>14.91</v>
       </c>
       <c r="E2" t="n">
         <v>16</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-21.7%</t>
+          <t>-20.5%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>453752</v>
+        <v>437369</v>
       </c>
       <c r="I2" t="n">
         <v>2.79</v>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -1048,23 +1048,23 @@
         <v>25.33</v>
       </c>
       <c r="D17" t="n">
-        <v>25.14</v>
+        <v>24.51</v>
       </c>
       <c r="E17" t="n">
         <v>24.8</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+1.4%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>27848</v>
+        <v>32091</v>
       </c>
       <c r="I17" t="n">
         <v>1.44</v>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -1381,23 +1381,23 @@
         <v>0.4845</v>
       </c>
       <c r="D26" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="E26" t="n">
         <v>0.443</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>35266</v>
+        <v>32650</v>
       </c>
       <c r="I26" t="n">
         <v>1.24</v>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -1011,23 +1011,23 @@
         <v>28.9</v>
       </c>
       <c r="D16" t="n">
-        <v>29.66</v>
+        <v>31.28</v>
       </c>
       <c r="E16" t="n">
         <v>34.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+2.6%</t>
+          <t>+8.2%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-14.0%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>19951</v>
+        <v>13931</v>
       </c>
       <c r="I16" t="n">
         <v>1.48</v>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -974,23 +974,23 @@
         <v>17.8</v>
       </c>
       <c r="D15" t="n">
-        <v>21.34</v>
+        <v>20.87</v>
       </c>
       <c r="E15" t="n">
         <v>27.98</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+19.9%</t>
+          <t>+17.2%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-23.7%</t>
+          <t>-25.4%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2798</v>
       </c>
       <c r="I15" t="n">
         <v>1.45</v>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -422,9 +422,9 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="33" customWidth="1" min="8" max="8"/>
@@ -493,23 +493,23 @@
         <v>18.76</v>
       </c>
       <c r="D2" t="n">
-        <v>14.91</v>
+        <v>15.98</v>
       </c>
       <c r="E2" t="n">
         <v>16</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-20.5%</t>
+          <t>-14.8%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>437369</v>
+        <v>358707</v>
       </c>
       <c r="I2" t="n">
         <v>2.79</v>
@@ -530,26 +530,26 @@
         <v>61.86</v>
       </c>
       <c r="D3" t="n">
-        <v>40.24</v>
+        <v>42.03</v>
       </c>
       <c r="E3" t="n">
         <v>45</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-34.9%</t>
+          <t>-32.1%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>421886</v>
+        <v>401319</v>
       </c>
       <c r="I3" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="4">
@@ -567,23 +567,23 @@
         <v>39.74</v>
       </c>
       <c r="D4" t="n">
-        <v>26.41</v>
+        <v>27.6</v>
       </c>
       <c r="E4" t="n">
         <v>30.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-33.5%</t>
+          <t>-30.5%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-13.4%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>440847</v>
+        <v>416150</v>
       </c>
       <c r="I4" t="n">
         <v>2.57</v>
@@ -601,29 +601,29 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>60.36015309349821</v>
+        <v>61.20482670023672</v>
       </c>
       <c r="D5" t="n">
-        <v>38.5</v>
+        <v>39.76</v>
       </c>
       <c r="E5" t="n">
-        <v>51.92762872993299</v>
+        <v>52.65429848142863</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-36.2%</t>
+          <t>-35.0%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-25.9%</t>
+          <t>-24.5%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>379056</v>
+        <v>380065</v>
       </c>
       <c r="I5" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="6">
@@ -789,26 +789,26 @@
         <v>76.08</v>
       </c>
       <c r="D10" t="n">
-        <v>73.34</v>
+        <v>73.16</v>
       </c>
       <c r="E10" t="n">
         <v>94</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-22.0%</t>
+          <t>-22.2%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>71456</v>
+        <v>72587</v>
       </c>
       <c r="I10" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="11">
@@ -826,23 +826,23 @@
         <v>7.51</v>
       </c>
       <c r="D11" t="n">
-        <v>5.99</v>
+        <v>5.98</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-20.3%</t>
+          <t>-20.4%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-40.1%</t>
+          <t>-40.2%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>94422</v>
+        <v>94534</v>
       </c>
       <c r="I11" t="n">
         <v>1.66</v>
@@ -863,23 +863,23 @@
         <v>29.49</v>
       </c>
       <c r="D12" t="n">
-        <v>30.94</v>
+        <v>30.87</v>
       </c>
       <c r="E12" t="n">
         <v>25</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+4.9%</t>
+          <t>+4.7%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+23.8%</t>
+          <t>+23.5%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>37928</v>
+        <v>38395</v>
       </c>
       <c r="I12" t="n">
         <v>1.67</v>
@@ -937,26 +937,26 @@
         <v>39.14</v>
       </c>
       <c r="D14" t="n">
-        <v>59.78</v>
+        <v>60.15</v>
       </c>
       <c r="E14" t="n">
         <v>51.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+52.7%</t>
+          <t>+53.7%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+16.1%</t>
+          <t>+16.8%</t>
         </is>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="15">
@@ -974,23 +974,23 @@
         <v>17.8</v>
       </c>
       <c r="D15" t="n">
-        <v>20.87</v>
+        <v>21.16</v>
       </c>
       <c r="E15" t="n">
         <v>27.98</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+17.2%</t>
+          <t>+18.9%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-25.4%</t>
+          <t>-24.4%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2798</v>
+        <v>949</v>
       </c>
       <c r="I15" t="n">
         <v>1.45</v>
@@ -1011,23 +1011,23 @@
         <v>28.9</v>
       </c>
       <c r="D16" t="n">
-        <v>31.28</v>
+        <v>31.84</v>
       </c>
       <c r="E16" t="n">
         <v>34.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+8.2%</t>
+          <t>+10.2%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>13931</v>
+        <v>11773</v>
       </c>
       <c r="I16" t="n">
         <v>1.48</v>
@@ -1048,23 +1048,23 @@
         <v>25.33</v>
       </c>
       <c r="D17" t="n">
-        <v>24.51</v>
+        <v>24.62</v>
       </c>
       <c r="E17" t="n">
         <v>24.8</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>32091</v>
+        <v>31433</v>
       </c>
       <c r="I17" t="n">
         <v>1.44</v>
@@ -1085,23 +1085,23 @@
         <v>13.9395</v>
       </c>
       <c r="D18" t="n">
-        <v>16.03</v>
+        <v>16.05</v>
       </c>
       <c r="E18" t="n">
         <v>18.9</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+15.0%</t>
+          <t>+15.1%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>-15.1%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>19107</v>
+        <v>18274</v>
       </c>
       <c r="I18" t="n">
         <v>2.46</v>
@@ -1196,19 +1196,19 @@
         <v>6.407</v>
       </c>
       <c r="D21" t="n">
-        <v>9.27</v>
+        <v>9.31</v>
       </c>
       <c r="E21" t="n">
         <v>7.13</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+44.7%</t>
+          <t>+45.3%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+30.0%</t>
+          <t>+30.6%</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1233,26 +1233,26 @@
         <v>16.29</v>
       </c>
       <c r="D22" t="n">
-        <v>15.57</v>
+        <v>15.83</v>
       </c>
       <c r="E22" t="n">
         <v>16.59</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>62034</v>
+        <v>57624</v>
       </c>
       <c r="I22" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="23">
@@ -1270,19 +1270,19 @@
         <v>7.6</v>
       </c>
       <c r="D23" t="n">
-        <v>9.699999999999999</v>
+        <v>10.21</v>
       </c>
       <c r="E23" t="n">
         <v>7.1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+27.6%</t>
+          <t>+34.3%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+36.6%</t>
+          <t>+43.8%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1393,11 +1393,11 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-9.8%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>32650</v>
+        <v>32599</v>
       </c>
       <c r="I26" t="n">
         <v>1.24</v>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -974,26 +974,26 @@
         <v>17.8</v>
       </c>
       <c r="D15" t="n">
-        <v>21.16</v>
+        <v>21.3</v>
       </c>
       <c r="E15" t="n">
         <v>27.98</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+18.9%</t>
+          <t>+19.6%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-24.4%</t>
+          <t>-23.9%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>949</v>
+        <v>930</v>
       </c>
       <c r="I15" t="n">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="16">
@@ -1011,26 +1011,26 @@
         <v>28.9</v>
       </c>
       <c r="D16" t="n">
-        <v>31.84</v>
+        <v>32.1</v>
       </c>
       <c r="E16" t="n">
         <v>34.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+10.2%</t>
+          <t>+11.1%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>11773</v>
+        <v>11492</v>
       </c>
       <c r="I16" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="17">
@@ -1048,26 +1048,26 @@
         <v>25.33</v>
       </c>
       <c r="D17" t="n">
-        <v>24.62</v>
+        <v>24.83</v>
       </c>
       <c r="E17" t="n">
         <v>24.8</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>+0.1%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>31433</v>
+        <v>30423</v>
       </c>
       <c r="I17" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="18">
@@ -1122,23 +1122,23 @@
         <v>2.5565</v>
       </c>
       <c r="D19" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="E19" t="n">
         <v>2.63</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-13.5%</t>
+          <t>-13.3%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>141591</v>
+        <v>139574</v>
       </c>
       <c r="I19" t="n">
         <v>1.32</v>
@@ -1159,26 +1159,26 @@
         <v>42.44</v>
       </c>
       <c r="D20" t="n">
-        <v>45.5</v>
+        <v>44.02</v>
       </c>
       <c r="E20" t="n">
         <v>52.04</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+7.2%</t>
+          <t>+3.7%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>16874</v>
+        <v>41213</v>
       </c>
       <c r="I20" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="21">
@@ -1233,26 +1233,26 @@
         <v>16.29</v>
       </c>
       <c r="D22" t="n">
-        <v>15.83</v>
+        <v>15.93</v>
       </c>
       <c r="E22" t="n">
         <v>16.59</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>57624</v>
+        <v>56053</v>
       </c>
       <c r="I22" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="23">
@@ -1270,26 +1270,26 @@
         <v>7.6</v>
       </c>
       <c r="D23" t="n">
-        <v>10.21</v>
+        <v>10.24</v>
       </c>
       <c r="E23" t="n">
         <v>7.1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+34.3%</t>
+          <t>+34.7%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+43.8%</t>
+          <t>+44.2%</t>
         </is>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="24">
@@ -1381,26 +1381,26 @@
         <v>0.4845</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="E26" t="n">
         <v>0.443</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>32599</v>
+        <v>28574</v>
       </c>
       <c r="I26" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -974,26 +974,26 @@
         <v>17.8</v>
       </c>
       <c r="D15" t="n">
-        <v>21.3</v>
+        <v>21.13</v>
       </c>
       <c r="E15" t="n">
         <v>27.98</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+19.6%</t>
+          <t>+18.7%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-24.5%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>930</v>
+        <v>1982</v>
       </c>
       <c r="I15" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="16">
@@ -1011,23 +1011,23 @@
         <v>28.9</v>
       </c>
       <c r="D16" t="n">
-        <v>32.1</v>
+        <v>31.88</v>
       </c>
       <c r="E16" t="n">
         <v>34.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+11.1%</t>
+          <t>+10.3%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>11492</v>
+        <v>12307</v>
       </c>
       <c r="I16" t="n">
         <v>1.36</v>
@@ -1048,23 +1048,23 @@
         <v>25.33</v>
       </c>
       <c r="D17" t="n">
-        <v>24.83</v>
+        <v>24.61</v>
       </c>
       <c r="E17" t="n">
         <v>24.8</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+0.1%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>30423</v>
+        <v>31845</v>
       </c>
       <c r="I17" t="n">
         <v>1.29</v>
@@ -1381,23 +1381,23 @@
         <v>0.4845</v>
       </c>
       <c r="D26" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="E26" t="n">
         <v>0.443</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>28574</v>
+        <v>29068</v>
       </c>
       <c r="I26" t="n">
         <v>1.17</v>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -424,7 +424,7 @@
     <col width="32" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="33" customWidth="1" min="8" max="8"/>
@@ -493,26 +493,26 @@
         <v>18.76</v>
       </c>
       <c r="D2" t="n">
-        <v>15.98</v>
+        <v>15.32</v>
       </c>
       <c r="E2" t="n">
         <v>16</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-14.8%</t>
+          <t>-18.4%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>358707</v>
+        <v>494031</v>
       </c>
       <c r="I2" t="n">
-        <v>2.79</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="3">
@@ -530,26 +530,26 @@
         <v>61.86</v>
       </c>
       <c r="D3" t="n">
-        <v>42.03</v>
+        <v>39.73</v>
       </c>
       <c r="E3" t="n">
         <v>45</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-32.1%</t>
+          <t>-35.8%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>401319</v>
+        <v>530104</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="4">
@@ -567,26 +567,26 @@
         <v>39.74</v>
       </c>
       <c r="D4" t="n">
-        <v>27.6</v>
+        <v>25.94</v>
       </c>
       <c r="E4" t="n">
         <v>30.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-30.5%</t>
+          <t>-34.7%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>416150</v>
+        <v>545468</v>
       </c>
       <c r="I4" t="n">
-        <v>2.57</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="5">
@@ -601,29 +601,29 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>61.20482670023672</v>
+        <v>60.02703358191058</v>
       </c>
       <c r="D5" t="n">
-        <v>39.76</v>
+        <v>37.59</v>
       </c>
       <c r="E5" t="n">
-        <v>52.65429848142863</v>
+        <v>51.64104717846436</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-35.0%</t>
+          <t>-37.4%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-24.5%</t>
+          <t>-27.2%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>380065</v>
+        <v>469118</v>
       </c>
       <c r="I5" t="n">
-        <v>2.36</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="6">
@@ -641,26 +641,26 @@
         <v>77.25</v>
       </c>
       <c r="D6" t="n">
-        <v>86.17</v>
+        <v>83.23</v>
       </c>
       <c r="E6" t="n">
         <v>75</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+11.6%</t>
+          <t>+7.7%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+14.9%</t>
+          <t>+11.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>8968</v>
+        <v>11451</v>
       </c>
       <c r="I6" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="7">
@@ -678,26 +678,26 @@
         <v>6.46</v>
       </c>
       <c r="D7" t="n">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="E7" t="n">
         <v>6</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-51.4%</t>
+          <t>-54.1%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-47.7%</t>
+          <t>-50.6%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>459263</v>
+        <v>620285</v>
       </c>
       <c r="I7" t="n">
-        <v>2.21</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="8">
@@ -789,26 +789,26 @@
         <v>76.08</v>
       </c>
       <c r="D10" t="n">
-        <v>73.16</v>
+        <v>72.23</v>
       </c>
       <c r="E10" t="n">
         <v>94</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-22.2%</t>
+          <t>-23.2%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>72587</v>
+        <v>67990</v>
       </c>
       <c r="I10" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="11">
@@ -826,26 +826,26 @@
         <v>7.51</v>
       </c>
       <c r="D11" t="n">
-        <v>5.98</v>
+        <v>5.71</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-20.4%</t>
+          <t>-23.9%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-40.2%</t>
+          <t>-42.9%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>94534</v>
+        <v>96485</v>
       </c>
       <c r="I11" t="n">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="12">
@@ -863,26 +863,26 @@
         <v>29.49</v>
       </c>
       <c r="D12" t="n">
-        <v>30.87</v>
+        <v>29.98</v>
       </c>
       <c r="E12" t="n">
         <v>25</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+4.7%</t>
+          <t>+1.7%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+23.5%</t>
+          <t>+19.9%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>38395</v>
+        <v>37671</v>
       </c>
       <c r="I12" t="n">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="13">
@@ -900,26 +900,26 @@
         <v>16.71</v>
       </c>
       <c r="D13" t="n">
-        <v>17.13</v>
+        <v>17.22</v>
       </c>
       <c r="E13" t="n">
         <v>17.95</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+2.5%</t>
+          <t>+3.1%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>21597</v>
+        <v>22102</v>
       </c>
       <c r="I13" t="n">
-        <v>1.38</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="14">
@@ -937,26 +937,26 @@
         <v>39.14</v>
       </c>
       <c r="D14" t="n">
-        <v>60.15</v>
+        <v>59.21</v>
       </c>
       <c r="E14" t="n">
         <v>51.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+53.7%</t>
+          <t>+51.3%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+16.8%</t>
+          <t>+15.0%</t>
         </is>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="15">
@@ -1085,26 +1085,26 @@
         <v>13.9395</v>
       </c>
       <c r="D18" t="n">
-        <v>16.05</v>
+        <v>15.1</v>
       </c>
       <c r="E18" t="n">
         <v>18.9</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+15.1%</t>
+          <t>+8.3%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-20.1%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>18274</v>
+        <v>27208</v>
       </c>
       <c r="I18" t="n">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="19">
@@ -1196,26 +1196,26 @@
         <v>6.407</v>
       </c>
       <c r="D21" t="n">
-        <v>9.31</v>
+        <v>8.83</v>
       </c>
       <c r="E21" t="n">
         <v>7.13</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+45.3%</t>
+          <t>+37.9%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+30.6%</t>
+          <t>+23.9%</t>
         </is>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>2.79</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="22">
@@ -1233,26 +1233,26 @@
         <v>16.29</v>
       </c>
       <c r="D22" t="n">
-        <v>15.93</v>
+        <v>15.65</v>
       </c>
       <c r="E22" t="n">
         <v>16.59</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>56053</v>
+        <v>61361</v>
       </c>
       <c r="I22" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="23">

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18.76</v>
+        <v>18.72</v>
       </c>
       <c r="D2" t="n">
         <v>15.32</v>
@@ -500,7 +500,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-18.4%</t>
+          <t>-18.2%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>494031</v>
+        <v>489951</v>
       </c>
       <c r="I2" t="n">
         <v>2.64</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>61.86</v>
+        <v>62.88</v>
       </c>
       <c r="D3" t="n">
         <v>39.73</v>
@@ -537,7 +537,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-35.8%</t>
+          <t>-36.8%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>530104</v>
+        <v>549197</v>
       </c>
       <c r="I3" t="n">
         <v>2.37</v>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>39.74</v>
+        <v>39.57</v>
       </c>
       <c r="D4" t="n">
         <v>25.94</v>
@@ -574,7 +574,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-34.7%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>545468</v>
+        <v>540231</v>
       </c>
       <c r="I4" t="n">
         <v>2.43</v>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>60.02703358191058</v>
+        <v>60.00754639429606</v>
       </c>
       <c r="D5" t="n">
         <v>37.59</v>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>469118</v>
+        <v>468801</v>
       </c>
       <c r="I5" t="n">
         <v>2.23</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>77.25</v>
+        <v>80.89</v>
       </c>
       <c r="D6" t="n">
         <v>83.23</v>
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+7.7%</t>
+          <t>+2.9%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>11451</v>
+        <v>49193</v>
       </c>
       <c r="I6" t="n">
         <v>1.78</v>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6.46</v>
+        <v>6.44</v>
       </c>
       <c r="D7" t="n">
         <v>2.97</v>
@@ -685,7 +685,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-54.1%</t>
+          <t>-54.0%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>620285</v>
+        <v>617242</v>
       </c>
       <c r="I7" t="n">
         <v>2.09</v>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>30.84</v>
+        <v>29.5</v>
       </c>
       <c r="D8" t="n">
         <v>28.16</v>
@@ -722,7 +722,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>207648</v>
+        <v>135338</v>
       </c>
       <c r="I8" t="n">
         <v>0.71</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.37</v>
+        <v>22.59</v>
       </c>
       <c r="D9" t="n">
         <v>29.97</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+34.0%</t>
+          <t>+32.7%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>76.08</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="D10" t="n">
         <v>72.23</v>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>67990</v>
+        <v>68460</v>
       </c>
       <c r="I10" t="n">
         <v>1.8</v>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7.51</v>
+        <v>7.49</v>
       </c>
       <c r="D11" t="n">
         <v>5.71</v>
@@ -833,7 +833,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-23.7%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>96485</v>
+        <v>95853</v>
       </c>
       <c r="I11" t="n">
         <v>1.79</v>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29.49</v>
+        <v>28.97</v>
       </c>
       <c r="D12" t="n">
         <v>29.98</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+1.7%</t>
+          <t>+3.5%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>37671</v>
+        <v>33992</v>
       </c>
       <c r="I12" t="n">
         <v>1.84</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.71</v>
+        <v>16.67</v>
       </c>
       <c r="D13" t="n">
         <v>17.22</v>
@@ -907,7 +907,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+3.1%</t>
+          <t>+3.3%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>22102</v>
+        <v>21702</v>
       </c>
       <c r="I13" t="n">
         <v>1.68</v>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>39.14</v>
+        <v>39.31</v>
       </c>
       <c r="D14" t="n">
         <v>59.21</v>
@@ -944,7 +944,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+51.3%</t>
+          <t>+50.6%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.8</v>
+        <v>17.68</v>
       </c>
       <c r="D15" t="n">
         <v>21.13</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+18.7%</t>
+          <t>+19.5%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1982</v>
+        <v>1244</v>
       </c>
       <c r="I15" t="n">
         <v>1.32</v>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>28.9</v>
+        <v>27.89</v>
       </c>
       <c r="D16" t="n">
         <v>31.88</v>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+10.3%</t>
+          <t>+14.3%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>12307</v>
+        <v>8480</v>
       </c>
       <c r="I16" t="n">
         <v>1.36</v>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>25.33</v>
+        <v>25.26</v>
       </c>
       <c r="D17" t="n">
         <v>24.61</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>31845</v>
+        <v>31418</v>
       </c>
       <c r="I17" t="n">
         <v>1.29</v>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>13.9395</v>
+        <v>14.306</v>
       </c>
       <c r="D18" t="n">
         <v>15.1</v>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+8.3%</t>
+          <t>+5.6%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>27208</v>
+        <v>53520</v>
       </c>
       <c r="I18" t="n">
         <v>2.32</v>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.5565</v>
+        <v>2.5462</v>
       </c>
       <c r="D19" t="n">
         <v>2.22</v>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-13.3%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>139574</v>
+        <v>136966</v>
       </c>
       <c r="I19" t="n">
         <v>1.32</v>
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>42.44</v>
+        <v>41.24</v>
       </c>
       <c r="D20" t="n">
         <v>44.02</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+3.7%</t>
+          <t>+6.7%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>41213</v>
+        <v>3362</v>
       </c>
       <c r="I20" t="n">
         <v>1.51</v>
@@ -1193,22 +1193,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6.407</v>
+        <v>6.2576</v>
       </c>
       <c r="D21" t="n">
-        <v>8.83</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="E21" t="n">
         <v>7.13</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+37.9%</t>
+          <t>+54.0%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+23.9%</t>
+          <t>+35.1%</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>16.29</v>
+        <v>16.75</v>
       </c>
       <c r="D22" t="n">
         <v>15.65</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>61361</v>
+        <v>69690</v>
       </c>
       <c r="I22" t="n">
         <v>1.59</v>
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7.6</v>
+        <v>7.46</v>
       </c>
       <c r="D23" t="n">
         <v>10.24</v>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+34.7%</t>
+          <t>+37.3%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>45.76</v>
+        <v>44.73</v>
       </c>
       <c r="D24" t="n">
         <v>33.93</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-25.9%</t>
+          <t>-24.1%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>223619</v>
+        <v>208723</v>
       </c>
       <c r="I24" t="n">
         <v>1.59</v>
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>21.6026</v>
+        <v>22.0806</v>
       </c>
       <c r="D25" t="n">
         <v>15.43</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-28.6%</t>
+          <t>-30.1%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>196627</v>
+        <v>207795</v>
       </c>
       <c r="I25" t="n">
         <v>1.59</v>
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.4845</v>
+        <v>0.39</v>
       </c>
       <c r="D26" t="n">
         <v>0.4</v>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>+3.3%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>29068</v>
+        <v>14262</v>
       </c>
       <c r="I26" t="n">
         <v>1.17</v>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -1051,7 +1051,7 @@
         <v>24.61</v>
       </c>
       <c r="E17" t="n">
-        <v>24.8</v>
+        <v>28.4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-13.3%</t>
         </is>
       </c>
       <c r="H17" t="n">

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18.72</v>
+        <v>19.52</v>
       </c>
       <c r="D2" t="n">
         <v>15.32</v>
@@ -500,7 +500,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-18.2%</t>
+          <t>-21.5%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>489951</v>
+        <v>571564</v>
       </c>
       <c r="I2" t="n">
         <v>2.64</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>62.88</v>
+        <v>60.29</v>
       </c>
       <c r="D3" t="n">
         <v>39.73</v>
@@ -537,7 +537,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-36.8%</t>
+          <t>-34.1%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>549197</v>
+        <v>500715</v>
       </c>
       <c r="I3" t="n">
         <v>2.37</v>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>39.57</v>
+        <v>41.21</v>
       </c>
       <c r="D4" t="n">
         <v>25.94</v>
@@ -574,7 +574,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-37.1%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>540231</v>
+        <v>590752</v>
       </c>
       <c r="I4" t="n">
         <v>2.43</v>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>60.00754639429606</v>
+        <v>63.04105193295555</v>
       </c>
       <c r="D5" t="n">
         <v>37.59</v>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-37.4%</t>
+          <t>-40.4%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>468801</v>
+        <v>518082</v>
       </c>
       <c r="I5" t="n">
         <v>2.23</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>80.89</v>
+        <v>85.13</v>
       </c>
       <c r="D6" t="n">
         <v>83.23</v>
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+2.9%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>49193</v>
+        <v>93157</v>
       </c>
       <c r="I6" t="n">
         <v>1.78</v>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6.44</v>
+        <v>6.71</v>
       </c>
       <c r="D7" t="n">
         <v>2.97</v>
@@ -685,7 +685,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-54.0%</t>
+          <t>-55.8%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>617242</v>
+        <v>658330</v>
       </c>
       <c r="I7" t="n">
         <v>2.09</v>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>29.5</v>
+        <v>30.8</v>
       </c>
       <c r="D8" t="n">
         <v>28.16</v>
@@ -722,7 +722,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>135338</v>
+        <v>205490</v>
       </c>
       <c r="I8" t="n">
         <v>0.71</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.59</v>
+        <v>22.61</v>
       </c>
       <c r="D9" t="n">
         <v>29.97</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+32.7%</t>
+          <t>+32.5%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>76.15000000000001</v>
+        <v>79.41</v>
       </c>
       <c r="D10" t="n">
         <v>72.23</v>
@@ -796,7 +796,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>68460</v>
+        <v>90377</v>
       </c>
       <c r="I10" t="n">
         <v>1.8</v>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7.49</v>
+        <v>7.74</v>
       </c>
       <c r="D11" t="n">
         <v>5.71</v>
@@ -833,7 +833,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-23.7%</t>
+          <t>-26.2%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>95853</v>
+        <v>103758</v>
       </c>
       <c r="I11" t="n">
         <v>1.79</v>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>28.97</v>
+        <v>30.08</v>
       </c>
       <c r="D12" t="n">
         <v>29.98</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+3.5%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>33992</v>
+        <v>41844</v>
       </c>
       <c r="I12" t="n">
         <v>1.84</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.67</v>
+        <v>17.61</v>
       </c>
       <c r="D13" t="n">
         <v>17.22</v>
@@ -907,7 +907,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+3.3%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>21702</v>
+        <v>31108</v>
       </c>
       <c r="I13" t="n">
         <v>1.68</v>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>39.31</v>
+        <v>41.45</v>
       </c>
       <c r="D14" t="n">
         <v>59.21</v>
@@ -944,7 +944,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+50.6%</t>
+          <t>+42.9%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.68</v>
+        <v>18.23</v>
       </c>
       <c r="D15" t="n">
         <v>21.13</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+19.5%</t>
+          <t>+15.9%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1244</v>
+        <v>4628</v>
       </c>
       <c r="I15" t="n">
         <v>1.32</v>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>27.89</v>
+        <v>29.05</v>
       </c>
       <c r="D16" t="n">
         <v>31.88</v>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+14.3%</t>
+          <t>+9.8%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>8480</v>
+        <v>12864</v>
       </c>
       <c r="I16" t="n">
         <v>1.36</v>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>25.26</v>
+        <v>26.34</v>
       </c>
       <c r="D17" t="n">
         <v>24.61</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>31418</v>
+        <v>38006</v>
       </c>
       <c r="I17" t="n">
         <v>1.29</v>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>14.306</v>
+        <v>14.6837</v>
       </c>
       <c r="D18" t="n">
         <v>15.1</v>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+5.6%</t>
+          <t>+2.9%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>53520</v>
+        <v>80462</v>
       </c>
       <c r="I18" t="n">
         <v>2.32</v>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.5462</v>
+        <v>2.7173</v>
       </c>
       <c r="D19" t="n">
         <v>2.22</v>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-18.4%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>136966</v>
+        <v>180285</v>
       </c>
       <c r="I19" t="n">
         <v>1.32</v>
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>41.24</v>
+        <v>42.17</v>
       </c>
       <c r="D20" t="n">
         <v>44.02</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+6.7%</t>
+          <t>+4.4%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>3362</v>
+        <v>32696</v>
       </c>
       <c r="I20" t="n">
         <v>1.51</v>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6.2576</v>
+        <v>6.7429</v>
       </c>
       <c r="D21" t="n">
         <v>9.630000000000001</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+54.0%</t>
+          <t>+42.9%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>16.75</v>
+        <v>17.24</v>
       </c>
       <c r="D22" t="n">
         <v>15.65</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-9.2%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>69690</v>
+        <v>78562</v>
       </c>
       <c r="I22" t="n">
         <v>1.59</v>
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7.46</v>
+        <v>7.75</v>
       </c>
       <c r="D23" t="n">
         <v>10.24</v>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+37.3%</t>
+          <t>+32.1%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>44.73</v>
+        <v>47.37</v>
       </c>
       <c r="D24" t="n">
         <v>33.93</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-24.1%</t>
+          <t>-28.4%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>208723</v>
+        <v>246904</v>
       </c>
       <c r="I24" t="n">
         <v>1.59</v>
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>22.0806</v>
+        <v>22.7519</v>
       </c>
       <c r="D25" t="n">
         <v>15.43</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-30.1%</t>
+          <t>-32.2%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>207795</v>
+        <v>223480</v>
       </c>
       <c r="I25" t="n">
         <v>1.59</v>
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.39</v>
+        <v>0.4951</v>
       </c>
       <c r="D26" t="n">
         <v>0.4</v>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+3.3%</t>
+          <t>-18.6%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>14262</v>
+        <v>30729</v>
       </c>
       <c r="I26" t="n">
         <v>1.17</v>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>19.52</v>
+        <v>19.17</v>
       </c>
       <c r="D2" t="n">
         <v>15.32</v>
@@ -500,7 +500,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-21.5%</t>
+          <t>-20.1%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>571564</v>
+        <v>535858</v>
       </c>
       <c r="I2" t="n">
         <v>2.64</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>60.29</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="D3" t="n">
         <v>39.73</v>
@@ -537,7 +537,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-34.1%</t>
+          <t>-38.9%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>500715</v>
+        <v>589629</v>
       </c>
       <c r="I3" t="n">
         <v>2.37</v>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>41.21</v>
+        <v>43.46</v>
       </c>
       <c r="D4" t="n">
         <v>25.94</v>
@@ -574,7 +574,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-37.1%</t>
+          <t>-40.3%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>590752</v>
+        <v>660065</v>
       </c>
       <c r="I4" t="n">
         <v>2.43</v>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>63.04105193295555</v>
+        <v>64.34019777392321</v>
       </c>
       <c r="D5" t="n">
         <v>37.59</v>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-40.4%</t>
+          <t>-41.6%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>518082</v>
+        <v>539187</v>
       </c>
       <c r="I5" t="n">
         <v>2.23</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>85.13</v>
+        <v>90.03</v>
       </c>
       <c r="D6" t="n">
         <v>83.23</v>
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>93157</v>
+        <v>143965</v>
       </c>
       <c r="I6" t="n">
         <v>1.78</v>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6.71</v>
+        <v>6.9</v>
       </c>
       <c r="D7" t="n">
         <v>2.97</v>
@@ -685,7 +685,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-55.8%</t>
+          <t>-57.0%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>658330</v>
+        <v>687243</v>
       </c>
       <c r="I7" t="n">
         <v>2.09</v>
@@ -712,26 +712,26 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>30.8</v>
+        <v>31.93</v>
       </c>
       <c r="D8" t="n">
-        <v>28.16</v>
+        <v>27.01</v>
       </c>
       <c r="E8" t="n">
         <v>25</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+12.7%</t>
+          <t>+8.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>205490</v>
+        <v>328633</v>
       </c>
       <c r="I8" t="n">
         <v>0.71</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.61</v>
+        <v>22.62</v>
       </c>
       <c r="D9" t="n">
         <v>29.97</v>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>79.41</v>
+        <v>77.2</v>
       </c>
       <c r="D10" t="n">
         <v>72.23</v>
@@ -796,7 +796,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>90377</v>
+        <v>75519</v>
       </c>
       <c r="I10" t="n">
         <v>1.8</v>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7.74</v>
+        <v>8.19</v>
       </c>
       <c r="D11" t="n">
         <v>5.71</v>
@@ -833,7 +833,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-26.2%</t>
+          <t>-30.2%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>103758</v>
+        <v>117987</v>
       </c>
       <c r="I11" t="n">
         <v>1.79</v>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>30.08</v>
+        <v>31.47</v>
       </c>
       <c r="D12" t="n">
         <v>29.98</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>41844</v>
+        <v>51677</v>
       </c>
       <c r="I12" t="n">
         <v>1.84</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.61</v>
+        <v>17.99</v>
       </c>
       <c r="D13" t="n">
         <v>17.22</v>
@@ -907,7 +907,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>31108</v>
+        <v>34911</v>
       </c>
       <c r="I13" t="n">
         <v>1.68</v>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>41.45</v>
+        <v>42.27</v>
       </c>
       <c r="D14" t="n">
         <v>59.21</v>
@@ -944,7 +944,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+42.9%</t>
+          <t>+40.1%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>18.23</v>
+        <v>20.6</v>
       </c>
       <c r="D15" t="n">
         <v>21.13</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+15.9%</t>
+          <t>+2.5%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>4628</v>
+        <v>19208</v>
       </c>
       <c r="I15" t="n">
         <v>1.32</v>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>29.05</v>
+        <v>31.11</v>
       </c>
       <c r="D16" t="n">
         <v>31.88</v>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+9.8%</t>
+          <t>+2.5%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>12864</v>
+        <v>20513</v>
       </c>
       <c r="I16" t="n">
         <v>1.36</v>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26.34</v>
+        <v>27.32</v>
       </c>
       <c r="D17" t="n">
         <v>24.61</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-9.9%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>38006</v>
+        <v>43985</v>
       </c>
       <c r="I17" t="n">
         <v>1.29</v>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>14.6837</v>
+        <v>16.5334</v>
       </c>
       <c r="D18" t="n">
         <v>15.1</v>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+2.9%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>80462</v>
+        <v>212404</v>
       </c>
       <c r="I18" t="n">
         <v>2.32</v>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.7173</v>
+        <v>3.0146</v>
       </c>
       <c r="D19" t="n">
         <v>2.22</v>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-18.4%</t>
+          <t>-26.4%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>180285</v>
+        <v>255556</v>
       </c>
       <c r="I19" t="n">
         <v>1.32</v>
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>42.17</v>
+        <v>45.3</v>
       </c>
       <c r="D20" t="n">
         <v>44.02</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+4.4%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>32696</v>
+        <v>131422</v>
       </c>
       <c r="I20" t="n">
         <v>1.51</v>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6.7429</v>
+        <v>6.32</v>
       </c>
       <c r="D21" t="n">
         <v>9.630000000000001</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+42.9%</t>
+          <t>+52.4%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>17.24</v>
+        <v>18.17</v>
       </c>
       <c r="D22" t="n">
         <v>15.65</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-9.2%</t>
+          <t>-13.9%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>78562</v>
+        <v>95400</v>
       </c>
       <c r="I22" t="n">
         <v>1.59</v>
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7.75</v>
+        <v>6.39</v>
       </c>
       <c r="D23" t="n">
         <v>10.24</v>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+32.1%</t>
+          <t>+60.2%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>47.37</v>
+        <v>50.79</v>
       </c>
       <c r="D24" t="n">
         <v>33.93</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-28.4%</t>
+          <t>-33.2%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>246904</v>
+        <v>296366</v>
       </c>
       <c r="I24" t="n">
         <v>1.59</v>
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>22.7519</v>
+        <v>25.0838</v>
       </c>
       <c r="D25" t="n">
         <v>15.43</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-32.2%</t>
+          <t>-38.5%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>223480</v>
+        <v>277962</v>
       </c>
       <c r="I25" t="n">
         <v>1.59</v>
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.4951</v>
+        <v>0.39</v>
       </c>
       <c r="D26" t="n">
         <v>0.4</v>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-18.6%</t>
+          <t>+3.3%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>30729</v>
+        <v>14262</v>
       </c>
       <c r="I26" t="n">
         <v>1.17</v>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>19.17</v>
+        <v>19.66</v>
       </c>
       <c r="D2" t="n">
         <v>15.32</v>
@@ -500,7 +500,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-20.1%</t>
+          <t>-22.1%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>535858</v>
+        <v>585846</v>
       </c>
       <c r="I2" t="n">
         <v>2.64</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>65.04000000000001</v>
+        <v>66.86</v>
       </c>
       <c r="D3" t="n">
         <v>39.73</v>
@@ -537,7 +537,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-38.9%</t>
+          <t>-40.6%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>589629</v>
+        <v>623698</v>
       </c>
       <c r="I3" t="n">
         <v>2.37</v>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>43.46</v>
+        <v>44.19</v>
       </c>
       <c r="D4" t="n">
         <v>25.94</v>
@@ -574,7 +574,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-40.3%</t>
+          <t>-41.3%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>660065</v>
+        <v>682553</v>
       </c>
       <c r="I4" t="n">
         <v>2.43</v>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>64.34019777392321</v>
+        <v>64.18430027300708</v>
       </c>
       <c r="D5" t="n">
         <v>37.59</v>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-41.6%</t>
+          <t>-41.4%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>539187</v>
+        <v>536654</v>
       </c>
       <c r="I5" t="n">
         <v>2.23</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>90.03</v>
+        <v>88.7</v>
       </c>
       <c r="D6" t="n">
         <v>83.23</v>
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>143965</v>
+        <v>130174</v>
       </c>
       <c r="I6" t="n">
         <v>1.78</v>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6.9</v>
+        <v>6.77</v>
       </c>
       <c r="D7" t="n">
         <v>2.97</v>
@@ -685,7 +685,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-57.0%</t>
+          <t>-56.2%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>687243</v>
+        <v>667460</v>
       </c>
       <c r="I7" t="n">
         <v>2.09</v>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>31.93</v>
+        <v>31.48</v>
       </c>
       <c r="D8" t="n">
         <v>27.01</v>
@@ -722,7 +722,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-14.2%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>328633</v>
+        <v>304350</v>
       </c>
       <c r="I8" t="n">
         <v>0.71</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.62</v>
+        <v>22.72</v>
       </c>
       <c r="D9" t="n">
         <v>29.97</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+32.5%</t>
+          <t>+31.9%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>77.2</v>
+        <v>78.03</v>
       </c>
       <c r="D10" t="n">
         <v>72.23</v>
@@ -796,7 +796,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>75519</v>
+        <v>81099</v>
       </c>
       <c r="I10" t="n">
         <v>1.8</v>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8.19</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="D11" t="n">
         <v>5.71</v>
@@ -833,7 +833,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-30.2%</t>
+          <t>-32.5%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>117987</v>
+        <v>126841</v>
       </c>
       <c r="I11" t="n">
         <v>1.79</v>
@@ -860,26 +860,26 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>31.47</v>
+        <v>32.62</v>
       </c>
       <c r="D12" t="n">
-        <v>29.98</v>
+        <v>32.14</v>
       </c>
       <c r="E12" t="n">
         <v>25</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+19.9%</t>
+          <t>+28.6%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>51677</v>
+        <v>43444</v>
       </c>
       <c r="I12" t="n">
         <v>1.84</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.99</v>
+        <v>17.36</v>
       </c>
       <c r="D13" t="n">
         <v>17.22</v>
@@ -907,7 +907,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>34911</v>
+        <v>28607</v>
       </c>
       <c r="I13" t="n">
         <v>1.68</v>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>42.27</v>
+        <v>42.52</v>
       </c>
       <c r="D14" t="n">
         <v>59.21</v>
@@ -944,7 +944,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+40.1%</t>
+          <t>+39.3%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>20.6</v>
+        <v>20.52</v>
       </c>
       <c r="D15" t="n">
         <v>21.13</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+2.5%</t>
+          <t>+2.9%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>19208</v>
+        <v>18716</v>
       </c>
       <c r="I15" t="n">
         <v>1.32</v>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>31.11</v>
+        <v>30.48</v>
       </c>
       <c r="D16" t="n">
         <v>31.88</v>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+2.5%</t>
+          <t>+4.6%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>20513</v>
+        <v>18174</v>
       </c>
       <c r="I16" t="n">
         <v>1.36</v>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>27.32</v>
+        <v>25.88</v>
       </c>
       <c r="D17" t="n">
         <v>24.61</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>43985</v>
+        <v>35200</v>
       </c>
       <c r="I17" t="n">
         <v>1.29</v>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.5334</v>
+        <v>16.4629</v>
       </c>
       <c r="D18" t="n">
         <v>15.1</v>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>212404</v>
+        <v>207375</v>
       </c>
       <c r="I18" t="n">
         <v>2.32</v>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3.0146</v>
+        <v>2.8535</v>
       </c>
       <c r="D19" t="n">
         <v>2.22</v>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-26.4%</t>
+          <t>-22.3%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>255556</v>
+        <v>214768</v>
       </c>
       <c r="I19" t="n">
         <v>1.32</v>
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>45.3</v>
+        <v>44.52</v>
       </c>
       <c r="D20" t="n">
         <v>44.02</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>131422</v>
+        <v>106820</v>
       </c>
       <c r="I20" t="n">
         <v>1.51</v>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6.32</v>
+        <v>4.9444</v>
       </c>
       <c r="D21" t="n">
         <v>9.630000000000001</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+52.4%</t>
+          <t>+94.9%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>18.17</v>
+        <v>18.35</v>
       </c>
       <c r="D22" t="n">
         <v>15.65</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-13.9%</t>
+          <t>-14.7%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>95400</v>
+        <v>98659</v>
       </c>
       <c r="I22" t="n">
         <v>1.59</v>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>50.79</v>
+        <v>49.78</v>
       </c>
       <c r="D24" t="n">
         <v>33.93</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-33.2%</t>
+          <t>-31.8%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>296366</v>
+        <v>281759</v>
       </c>
       <c r="I24" t="n">
         <v>1.59</v>
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>25.0838</v>
+        <v>24.0493</v>
       </c>
       <c r="D25" t="n">
         <v>15.43</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-38.5%</t>
+          <t>-35.8%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>277962</v>
+        <v>253792</v>
       </c>
       <c r="I25" t="n">
         <v>1.59</v>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -1196,23 +1196,23 @@
         <v>4.9444</v>
       </c>
       <c r="D21" t="n">
-        <v>9.630000000000001</v>
+        <v>4.7</v>
       </c>
       <c r="E21" t="n">
-        <v>7.13</v>
+        <v>4.56</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+94.9%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+35.1%</t>
+          <t>+3.0%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>203013</v>
       </c>
       <c r="I21" t="n">
         <v>2.64</v>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -1051,7 +1051,7 @@
         <v>24.61</v>
       </c>
       <c r="E17" t="n">
-        <v>28.4</v>
+        <v>27.2</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-13.3%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.4629</v>
+        <v>16.4636</v>
       </c>
       <c r="D18" t="n">
         <v>15.1</v>
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>207375</v>
+        <v>207425</v>
       </c>
       <c r="I18" t="n">
         <v>2.32</v>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.8535</v>
+        <v>2.8536</v>
       </c>
       <c r="D19" t="n">
         <v>2.22</v>
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>214768</v>
+        <v>214794</v>
       </c>
       <c r="I19" t="n">
         <v>1.32</v>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4.9444</v>
+        <v>4.9446</v>
       </c>
       <c r="D21" t="n">
         <v>4.7</v>
@@ -1212,7 +1212,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>203013</v>
+        <v>203062</v>
       </c>
       <c r="I21" t="n">
         <v>2.64</v>
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6.39</v>
+        <v>8.52</v>
       </c>
       <c r="D23" t="n">
         <v>10.24</v>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+60.2%</t>
+          <t>+20.2%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24.0493</v>
+        <v>24.0503</v>
       </c>
       <c r="D25" t="n">
         <v>15.43</v>
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>253792</v>
+        <v>253816</v>
       </c>
       <c r="I25" t="n">
         <v>1.59</v>
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.39</v>
+        <v>0.5326</v>
       </c>
       <c r="D26" t="n">
         <v>0.4</v>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+3.3%</t>
+          <t>-24.4%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>14262</v>
+        <v>36604</v>
       </c>
       <c r="I26" t="n">
         <v>1.17</v>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -974,26 +974,26 @@
         <v>20.52</v>
       </c>
       <c r="D15" t="n">
-        <v>21.13</v>
+        <v>21.48</v>
       </c>
       <c r="E15" t="n">
         <v>27.98</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+2.9%</t>
+          <t>+4.7%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-24.5%</t>
+          <t>-23.2%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>18716</v>
+        <v>18156</v>
       </c>
       <c r="I15" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="16">
@@ -1011,26 +1011,26 @@
         <v>30.48</v>
       </c>
       <c r="D16" t="n">
-        <v>31.88</v>
+        <v>32.46</v>
       </c>
       <c r="E16" t="n">
         <v>34.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+4.6%</t>
+          <t>+6.5%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>18174</v>
+        <v>17725</v>
       </c>
       <c r="I16" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="17">
@@ -1048,26 +1048,26 @@
         <v>25.88</v>
       </c>
       <c r="D17" t="n">
-        <v>24.61</v>
+        <v>25.02</v>
       </c>
       <c r="E17" t="n">
         <v>27.2</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>35200</v>
+        <v>34989</v>
       </c>
       <c r="I17" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="18">
@@ -1233,26 +1233,26 @@
         <v>18.35</v>
       </c>
       <c r="D22" t="n">
-        <v>15.65</v>
+        <v>15.83</v>
       </c>
       <c r="E22" t="n">
         <v>16.59</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-14.7%</t>
+          <t>-13.7%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>98659</v>
+        <v>96705</v>
       </c>
       <c r="I22" t="n">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="23">
@@ -1270,26 +1270,26 @@
         <v>8.52</v>
       </c>
       <c r="D23" t="n">
-        <v>10.24</v>
+        <v>10.34</v>
       </c>
       <c r="E23" t="n">
         <v>7.1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+20.2%</t>
+          <t>+21.4%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+44.2%</t>
+          <t>+45.7%</t>
         </is>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="24">
@@ -1381,26 +1381,26 @@
         <v>0.5326</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="E26" t="n">
         <v>0.443</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-24.4%</t>
+          <t>-23.8%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>36604</v>
+        <v>40554</v>
       </c>
       <c r="I26" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-23.9%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>40554</v>
+        <v>40559</v>
       </c>
       <c r="I26" t="n">
         <v>1.2</v>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -1122,23 +1122,23 @@
         <v>2.8536</v>
       </c>
       <c r="D19" t="n">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="E19" t="n">
         <v>2.63</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-22.3%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>214794</v>
+        <v>192190</v>
       </c>
       <c r="I19" t="n">
         <v>1.32</v>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -567,26 +567,26 @@
         <v>44.19</v>
       </c>
       <c r="D4" t="n">
-        <v>25.94</v>
+        <v>26.58</v>
       </c>
       <c r="E4" t="n">
         <v>30.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-41.3%</t>
+          <t>-39.8%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>682553</v>
+        <v>715733</v>
       </c>
       <c r="I4" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="5">
@@ -678,23 +678,23 @@
         <v>6.77</v>
       </c>
       <c r="D7" t="n">
-        <v>2.97</v>
+        <v>2.89</v>
       </c>
       <c r="E7" t="n">
         <v>6</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-56.2%</t>
+          <t>-57.3%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-50.6%</t>
+          <t>-51.8%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>667460</v>
+        <v>678594</v>
       </c>
       <c r="I7" t="n">
         <v>2.09</v>
@@ -826,26 +826,26 @@
         <v>8.470000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>5.71</v>
+        <v>4.83</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-32.5%</t>
+          <t>-43.0%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-42.9%</t>
+          <t>-51.7%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>126841</v>
+        <v>159436</v>
       </c>
       <c r="I11" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="12">
@@ -1344,23 +1344,23 @@
         <v>24.0503</v>
       </c>
       <c r="D25" t="n">
-        <v>15.43</v>
+        <v>15.48</v>
       </c>
       <c r="E25" t="n">
         <v>17.52</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-35.8%</t>
+          <t>-35.6%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>253816</v>
+        <v>252777</v>
       </c>
       <c r="I25" t="n">
         <v>1.59</v>

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -1085,26 +1085,26 @@
         <v>16.4636</v>
       </c>
       <c r="D18" t="n">
-        <v>15.1</v>
+        <v>16.95</v>
       </c>
       <c r="E18" t="n">
         <v>18.9</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>+2.9%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-20.1%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>207425</v>
+        <v>63532</v>
       </c>
       <c r="I18" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="19">

--- a/outputs/fair_value_summary.xlsx
+++ b/outputs/fair_value_summary.xlsx
@@ -974,26 +974,26 @@
         <v>20.52</v>
       </c>
       <c r="D15" t="n">
-        <v>21.48</v>
+        <v>21.83</v>
       </c>
       <c r="E15" t="n">
         <v>27.98</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+4.7%</t>
+          <t>+6.4%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-23.2%</t>
+          <t>-22.0%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>18156</v>
+        <v>16931</v>
       </c>
       <c r="I15" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="16">
@@ -1011,26 +1011,26 @@
         <v>30.48</v>
       </c>
       <c r="D16" t="n">
-        <v>32.46</v>
+        <v>32.67</v>
       </c>
       <c r="E16" t="n">
         <v>34.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+6.5%</t>
+          <t>+7.2%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>17725</v>
+        <v>15280</v>
       </c>
       <c r="I16" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="17">
@@ -1048,26 +1048,26 @@
         <v>25.88</v>
       </c>
       <c r="D17" t="n">
-        <v>25.02</v>
+        <v>25.42</v>
       </c>
       <c r="E17" t="n">
         <v>27.2</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>34989</v>
+        <v>34013</v>
       </c>
       <c r="I17" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="18">
@@ -1233,26 +1233,26 @@
         <v>18.35</v>
       </c>
       <c r="D22" t="n">
-        <v>15.83</v>
+        <v>15.94</v>
       </c>
       <c r="E22" t="n">
         <v>16.59</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-13.7%</t>
+          <t>-13.1%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>96705</v>
+        <v>96085</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="23">
@@ -1270,26 +1270,26 @@
         <v>8.52</v>
       </c>
       <c r="D23" t="n">
-        <v>10.34</v>
+        <v>10.42</v>
       </c>
       <c r="E23" t="n">
         <v>7.1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+21.4%</t>
+          <t>+22.3%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+45.7%</t>
+          <t>+46.8%</t>
         </is>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="24">
@@ -1388,19 +1388,19 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-22.8%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>40559</v>
+        <v>40189</v>
       </c>
       <c r="I26" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>
